--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -258,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -361,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -428,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -604,2519 +350,2628 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.1007852441846325</v>
+        <v>0.1008553302131494</v>
       </c>
       <c r="C2">
-        <v>0.1146841523906033</v>
+        <v>0.1148604146349085</v>
       </c>
       <c r="D2">
-        <v>0.1170758037848568</v>
+        <v>0.1170982346407076</v>
       </c>
       <c r="E2">
-        <v>0.1169221418186755</v>
+        <v>0.1169317529166724</v>
       </c>
       <c r="F2">
-        <v>0.11625425849269259</v>
+        <v>0.1160000982886547</v>
       </c>
       <c r="G2">
-        <v>0.1172454663289501</v>
+        <v>0.116987748319196</v>
       </c>
       <c r="H2">
-        <v>0.1175171364482198</v>
+        <v>0.117251423560506</v>
       </c>
       <c r="I2">
-        <v>0.1138784991074924</v>
+        <v>0.1139004428754559</v>
       </c>
       <c r="J2">
-        <v>0.1108346653652189</v>
+        <v>0.1106991700098848</v>
       </c>
       <c r="K2">
-        <v>0.11317313907855681</v>
+        <v>0.1127464869054649</v>
       </c>
       <c r="L2">
-        <v>0.11037492607055339</v>
+        <v>0.1102562623746369</v>
       </c>
       <c r="M2">
-        <v>0.1049962779023474</v>
+        <v>0.1054083757277418</v>
       </c>
       <c r="N2">
-        <v>0.10348427967404911</v>
+        <v>0.1035771817704613</v>
       </c>
       <c r="O2">
-        <v>9.6832955297533843E-2</v>
+        <v>0.09684953339418387</v>
       </c>
       <c r="P2">
-        <v>9.0957378677747072E-2</v>
+        <v>0.09105120627700392</v>
       </c>
       <c r="Q2">
-        <v>8.829149553948111E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.08816649166567267</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.10388472362736351</v>
+        <v>0.1046889852578794</v>
       </c>
       <c r="C3">
-        <v>0.11313555839483939</v>
+        <v>0.1132405395908314</v>
       </c>
       <c r="D3">
-        <v>0.122365002573433</v>
+        <v>0.1226386180505925</v>
       </c>
       <c r="E3">
-        <v>0.1191814036522174</v>
+        <v>0.1191524089712133</v>
       </c>
       <c r="F3">
-        <v>0.1113032629428207</v>
+        <v>0.111249982395368</v>
       </c>
       <c r="G3">
-        <v>0.1068241066921109</v>
+        <v>0.1063620934834092</v>
       </c>
       <c r="H3">
-        <v>0.1030043356717984</v>
+        <v>0.1031517924539951</v>
       </c>
       <c r="I3">
-        <v>9.9220493571592391E-2</v>
+        <v>0.09965434767678219</v>
       </c>
       <c r="J3">
-        <v>9.7478249827449265E-2</v>
+        <v>0.09812185646522047</v>
       </c>
       <c r="K3">
-        <v>9.4225865768828271E-2</v>
+        <v>0.0951237808269354</v>
       </c>
       <c r="L3">
-        <v>9.1862464271563693E-2</v>
+        <v>0.09301315210451752</v>
       </c>
       <c r="M3">
-        <v>9.2637303716999103E-2</v>
+        <v>0.09331185467844615</v>
       </c>
       <c r="N3">
-        <v>9.2671467332134008E-2</v>
+        <v>0.09356379714924005</v>
       </c>
       <c r="O3">
-        <v>9.467397663855695E-2</v>
+        <v>0.09545159901650838</v>
       </c>
       <c r="P3">
-        <v>9.6067957606555079E-2</v>
+        <v>0.09609359084632343</v>
       </c>
       <c r="Q3">
-        <v>9.4911402479220891E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.09494617393796725</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.1070959477420972</v>
+        <v>0.1072362495134301</v>
       </c>
       <c r="C4">
-        <v>0.1143542858978394</v>
+        <v>0.1143122190390259</v>
       </c>
       <c r="D4">
-        <v>0.11568040331189421</v>
+        <v>0.1153076252588807</v>
       </c>
       <c r="E4">
-        <v>0.1197562744555002</v>
+        <v>0.1193045173305053</v>
       </c>
       <c r="F4">
-        <v>0.120144689006955</v>
+        <v>0.1191354603808063</v>
       </c>
       <c r="G4">
-        <v>0.1230682979251639</v>
+        <v>0.1221183466730168</v>
       </c>
       <c r="H4">
-        <v>0.1168969172049269</v>
+        <v>0.1164489693260793</v>
       </c>
       <c r="I4">
-        <v>0.11215318387885061</v>
+        <v>0.1111712165036118</v>
       </c>
       <c r="J4">
-        <v>0.1095144352939833</v>
+        <v>0.108547895250518</v>
       </c>
       <c r="K4">
-        <v>0.10911820790375221</v>
+        <v>0.1084885269668619</v>
       </c>
       <c r="L4">
-        <v>0.1042414267381116</v>
+        <v>0.1044487595234194</v>
       </c>
       <c r="M4">
-        <v>9.996284613257081E-2</v>
+        <v>0.09984785201819911</v>
       </c>
       <c r="N4">
-        <v>9.5672668279804765E-2</v>
+        <v>0.09568982722875033</v>
       </c>
       <c r="O4">
-        <v>9.3637909826237667E-2</v>
+        <v>0.09355851113328763</v>
       </c>
       <c r="P4">
-        <v>9.3435216937669346E-2</v>
+        <v>0.09330209288631988</v>
       </c>
       <c r="Q4">
-        <v>9.4672838114924815E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.09437705407006808</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>9.8202717141486678E-2</v>
+        <v>0.09802731676055335</v>
       </c>
       <c r="C5">
-        <v>0.1137504014741723</v>
+        <v>0.1137771338278501</v>
       </c>
       <c r="D5">
-        <v>0.1171601953446266</v>
+        <v>0.117817984162642</v>
       </c>
       <c r="E5">
-        <v>0.1151126958484206</v>
+        <v>0.1149281393249069</v>
       </c>
       <c r="F5">
-        <v>0.1203239614730709</v>
+        <v>0.1201881694516398</v>
       </c>
       <c r="G5">
-        <v>0.1092058658568163</v>
+        <v>0.1093553314730501</v>
       </c>
       <c r="H5">
-        <v>0.10336789910994371</v>
+        <v>0.1037656995695686</v>
       </c>
       <c r="I5">
-        <v>0.1016418871774635</v>
+        <v>0.1019911391760397</v>
       </c>
       <c r="J5">
-        <v>9.7286114783863356E-2</v>
+        <v>0.09732361754928549</v>
       </c>
       <c r="K5">
-        <v>9.2083018431809549E-2</v>
+        <v>0.09239635594200374</v>
       </c>
       <c r="L5">
-        <v>9.0068609153784215E-2</v>
+        <v>0.09027850230263419</v>
       </c>
       <c r="M5">
-        <v>8.7623753979773761E-2</v>
+        <v>0.08835624352805323</v>
       </c>
       <c r="N5">
-        <v>8.7405888154798508E-2</v>
+        <v>0.08858376222229541</v>
       </c>
       <c r="O5">
-        <v>8.8955015036136023E-2</v>
+        <v>0.09051240722079215</v>
       </c>
       <c r="P5">
-        <v>9.0284534912080106E-2</v>
+        <v>0.09203276478502925</v>
       </c>
       <c r="Q5">
-        <v>9.2283353113044822E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.09368309776316465</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>9.3844383434330783E-2</v>
+        <v>0.09337746042849331</v>
       </c>
       <c r="C6">
-        <v>0.11382137845294189</v>
+        <v>0.1142218325778378</v>
       </c>
       <c r="D6">
-        <v>0.1185880798091213</v>
+        <v>0.1187731307719691</v>
       </c>
       <c r="E6">
-        <v>0.1158986909618737</v>
+        <v>0.1160263344959161</v>
       </c>
       <c r="F6">
-        <v>0.1177581467630146</v>
+        <v>0.1176719096807987</v>
       </c>
       <c r="G6">
-        <v>0.10537258353019301</v>
+        <v>0.1048595597549985</v>
       </c>
       <c r="H6">
-        <v>9.9777410865414931E-2</v>
+        <v>0.09907313787045703</v>
       </c>
       <c r="I6">
-        <v>9.65267175252571E-2</v>
+        <v>0.09529597331330948</v>
       </c>
       <c r="J6">
-        <v>9.1351061024972077E-2</v>
+        <v>0.09049668198820184</v>
       </c>
       <c r="K6">
-        <v>8.8250258729233075E-2</v>
+        <v>0.0875303651310365</v>
       </c>
       <c r="L6">
-        <v>8.7240436437322308E-2</v>
+        <v>0.08640637609268483</v>
       </c>
       <c r="M6">
-        <v>8.5838702350393328E-2</v>
+        <v>0.08492586891853143</v>
       </c>
       <c r="N6">
-        <v>8.5239663496850901E-2</v>
+        <v>0.08496816369416786</v>
       </c>
       <c r="O6">
-        <v>8.596995412822582E-2</v>
+        <v>0.08561891835141473</v>
       </c>
       <c r="P6">
-        <v>8.5654241456469743E-2</v>
+        <v>0.08534467109291174</v>
       </c>
       <c r="Q6">
-        <v>8.7287045401441582E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.08677607252043083</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.1060778729718508</v>
+        <v>0.1064714022795334</v>
       </c>
       <c r="C7">
-        <v>0.11439813343174859</v>
+        <v>0.1146523710394368</v>
       </c>
       <c r="D7">
-        <v>0.1155070864933339</v>
+        <v>0.1159857369623651</v>
       </c>
       <c r="E7">
-        <v>0.1191431048103653</v>
+        <v>0.1196115401185697</v>
       </c>
       <c r="F7">
-        <v>0.12035946248413749</v>
+        <v>0.1209090527164597</v>
       </c>
       <c r="G7">
-        <v>0.1238403906910317</v>
+        <v>0.1241201407997516</v>
       </c>
       <c r="H7">
-        <v>0.1213154181246095</v>
+        <v>0.1217342512298871</v>
       </c>
       <c r="I7">
-        <v>0.1147813785165247</v>
+        <v>0.1152804906214999</v>
       </c>
       <c r="J7">
-        <v>0.1102593328909643</v>
+        <v>0.1101714141491665</v>
       </c>
       <c r="K7">
-        <v>0.1084115834942337</v>
+        <v>0.1085314306155861</v>
       </c>
       <c r="L7">
-        <v>0.1071512351625724</v>
+        <v>0.1075095049985089</v>
       </c>
       <c r="M7">
-        <v>0.1012830127550699</v>
+        <v>0.1021525334426141</v>
       </c>
       <c r="N7">
-        <v>9.6596967733343281E-2</v>
+        <v>0.09742549030221814</v>
       </c>
       <c r="O7">
-        <v>9.3442647531230147E-2</v>
+        <v>0.09417967207526218</v>
       </c>
       <c r="P7">
-        <v>9.2050844618911123E-2</v>
+        <v>0.09226052607390395</v>
       </c>
       <c r="Q7">
-        <v>9.1648187144715482E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.09192515196000554</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.1016671681074518</v>
+        <v>0.1026903328296165</v>
       </c>
       <c r="C8">
-        <v>0.1142435696664668</v>
+        <v>0.1142447188674363</v>
       </c>
       <c r="D8">
-        <v>0.115965942795311</v>
+        <v>0.1158193611373985</v>
       </c>
       <c r="E8">
-        <v>0.12006101125516649</v>
+        <v>0.1195905055557177</v>
       </c>
       <c r="F8">
-        <v>0.122032369546426</v>
+        <v>0.1217796573240957</v>
       </c>
       <c r="G8">
-        <v>0.11886462690733859</v>
+        <v>0.1182598618590907</v>
       </c>
       <c r="H8">
-        <v>0.1124113213305931</v>
+        <v>0.1125589859569435</v>
       </c>
       <c r="I8">
-        <v>0.111469432410227</v>
+        <v>0.1117627666731298</v>
       </c>
       <c r="J8">
-        <v>0.1057449851182502</v>
+        <v>0.1057672021856223</v>
       </c>
       <c r="K8">
-        <v>0.10290635652223069</v>
+        <v>0.1034922956126765</v>
       </c>
       <c r="L8">
-        <v>9.5710379688392772E-2</v>
+        <v>0.09591984596272006</v>
       </c>
       <c r="M8">
-        <v>9.5150872891888685E-2</v>
+        <v>0.09457566258930843</v>
       </c>
       <c r="N8">
-        <v>9.1666935869495939E-2</v>
+        <v>0.09151310381792929</v>
       </c>
       <c r="O8">
-        <v>8.9774831214949891E-2</v>
+        <v>0.0898381597586549</v>
       </c>
       <c r="P8">
-        <v>8.9872083085247217E-2</v>
+        <v>0.08982931530329619</v>
       </c>
       <c r="Q8">
-        <v>9.0783752018413461E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.09102746654555567</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>9.8826563426016992E-2</v>
+        <v>0.09784703362082237</v>
       </c>
       <c r="C9">
-        <v>0.1140819783025576</v>
+        <v>0.1139401661812223</v>
       </c>
       <c r="D9">
-        <v>0.1155971603095421</v>
+        <v>0.115581047819384</v>
       </c>
       <c r="E9">
-        <v>0.1191101163555322</v>
+        <v>0.1191967450099261</v>
       </c>
       <c r="F9">
-        <v>0.12047306090332301</v>
+        <v>0.1204414279659199</v>
       </c>
       <c r="G9">
-        <v>0.1177089886807407</v>
+        <v>0.1178147596679511</v>
       </c>
       <c r="H9">
-        <v>0.1120448881628243</v>
+        <v>0.1120573715190038</v>
       </c>
       <c r="I9">
-        <v>0.11159345331491199</v>
+        <v>0.1112034872923437</v>
       </c>
       <c r="J9">
-        <v>0.1058214794292479</v>
+        <v>0.1055007380943934</v>
       </c>
       <c r="K9">
-        <v>0.1037922632491227</v>
+        <v>0.1036533682937286</v>
       </c>
       <c r="L9">
-        <v>9.4375097431789082E-2</v>
+        <v>0.09394670086247843</v>
       </c>
       <c r="M9">
-        <v>9.463179677484905E-2</v>
+        <v>0.09418274530936577</v>
       </c>
       <c r="N9">
-        <v>9.1501478541021891E-2</v>
+        <v>0.09116753304325097</v>
       </c>
       <c r="O9">
-        <v>8.96066558979116E-2</v>
+        <v>0.0891495471975343</v>
       </c>
       <c r="P9">
-        <v>8.9676015982249321E-2</v>
+        <v>0.08961729606372015</v>
       </c>
       <c r="Q9">
-        <v>8.9772508083163297E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.08969607854386755</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.1003973835700952</v>
+        <v>0.09965230724602493</v>
       </c>
       <c r="C10">
-        <v>0.1143210421068621</v>
+        <v>0.1143951684038228</v>
       </c>
       <c r="D10">
-        <v>0.11598159600836221</v>
+        <v>0.1157742410266587</v>
       </c>
       <c r="E10">
-        <v>0.1194575279785841</v>
+        <v>0.1192917647814444</v>
       </c>
       <c r="F10">
-        <v>0.12126015602368929</v>
+        <v>0.1209811391446332</v>
       </c>
       <c r="G10">
-        <v>0.11862204075208881</v>
+        <v>0.1181640244835191</v>
       </c>
       <c r="H10">
-        <v>0.1125748396095544</v>
+        <v>0.1127232403465558</v>
       </c>
       <c r="I10">
-        <v>0.1119553451952631</v>
+        <v>0.1114836332365461</v>
       </c>
       <c r="J10">
-        <v>0.10579080955203531</v>
+        <v>0.1061330557833374</v>
       </c>
       <c r="K10">
-        <v>0.104423799557393</v>
+        <v>0.104520162553899</v>
       </c>
       <c r="L10">
-        <v>9.4813671633118032E-2</v>
+        <v>0.09414557968090675</v>
       </c>
       <c r="M10">
-        <v>9.5568347459943817E-2</v>
+        <v>0.09535643733177424</v>
       </c>
       <c r="N10">
-        <v>9.2845152116452584E-2</v>
+        <v>0.09234631433074816</v>
       </c>
       <c r="O10">
-        <v>9.1172692719770673E-2</v>
+        <v>0.09009019957148538</v>
       </c>
       <c r="P10">
-        <v>9.1323022256321093E-2</v>
+        <v>0.09074325822736874</v>
       </c>
       <c r="Q10">
-        <v>9.1257390535347233E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.09056572964223722</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>9.8095935806904219E-2</v>
+        <v>0.09812794132718636</v>
       </c>
       <c r="C11">
-        <v>0.1141540800172146</v>
+        <v>0.1141392543708036</v>
       </c>
       <c r="D11">
-        <v>0.115684606022091</v>
+        <v>0.1158029066379898</v>
       </c>
       <c r="E11">
-        <v>0.11938956485100589</v>
+        <v>0.1196165947335094</v>
       </c>
       <c r="F11">
-        <v>0.1205192835750651</v>
+        <v>0.121517774959299</v>
       </c>
       <c r="G11">
-        <v>0.1183671632364405</v>
+        <v>0.1187850781913221</v>
       </c>
       <c r="H11">
-        <v>0.11258180883255819</v>
+        <v>0.1125795030429857</v>
       </c>
       <c r="I11">
-        <v>0.11223161145348121</v>
+        <v>0.1122529890821305</v>
       </c>
       <c r="J11">
-        <v>0.1062480530590889</v>
+        <v>0.1060168136027072</v>
       </c>
       <c r="K11">
-        <v>0.10445916424857909</v>
+        <v>0.1041035149728257</v>
       </c>
       <c r="L11">
-        <v>9.4382123414349872E-2</v>
+        <v>0.0942192479157548</v>
       </c>
       <c r="M11">
-        <v>9.4078109649059757E-2</v>
+        <v>0.09405831697586151</v>
       </c>
       <c r="N11">
-        <v>9.0994833779555209E-2</v>
+        <v>0.0912082994034835</v>
       </c>
       <c r="O11">
-        <v>8.9190830680720007E-2</v>
+        <v>0.08961341610928832</v>
       </c>
       <c r="P11">
-        <v>8.9639623817287795E-2</v>
+        <v>0.0898780228084385</v>
       </c>
       <c r="Q11">
-        <v>8.9624536188364454E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.09009603009540193</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>9.330712063746946E-2</v>
+        <v>0.09333719583756321</v>
       </c>
       <c r="C12">
-        <v>0.114116683735554</v>
+        <v>0.113859295227354</v>
       </c>
       <c r="D12">
-        <v>0.11765650569053961</v>
+        <v>0.1178126044358169</v>
       </c>
       <c r="E12">
-        <v>0.11521846419197081</v>
+        <v>0.1149174101629243</v>
       </c>
       <c r="F12">
-        <v>0.1197623744900482</v>
+        <v>0.1204209362340379</v>
       </c>
       <c r="G12">
-        <v>0.10955844717439329</v>
+        <v>0.1104011934057718</v>
       </c>
       <c r="H12">
-        <v>0.1062389192038336</v>
+        <v>0.1066104734993591</v>
       </c>
       <c r="I12">
-        <v>9.9554562443298897E-2</v>
+        <v>0.09998162384167045</v>
       </c>
       <c r="J12">
-        <v>9.2724209287451051E-2</v>
+        <v>0.09269408900617872</v>
       </c>
       <c r="K12">
-        <v>8.8562113575253384E-2</v>
+        <v>0.08845438477035161</v>
       </c>
       <c r="L12">
-        <v>8.6395993027279044E-2</v>
+        <v>0.08627571140577991</v>
       </c>
       <c r="M12">
-        <v>8.414906854994729E-2</v>
+        <v>0.08387739224074835</v>
       </c>
       <c r="N12">
-        <v>8.381155417675866E-2</v>
+        <v>0.08359797540672678</v>
       </c>
       <c r="O12">
-        <v>8.5338845885774728E-2</v>
+        <v>0.08496581711531383</v>
       </c>
       <c r="P12">
-        <v>8.6826058380217522E-2</v>
+        <v>0.08660235456802311</v>
       </c>
       <c r="Q12">
-        <v>8.9595860134257049E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.08903813278613341</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.11102095748364819</v>
+        <v>0.1115737854198935</v>
       </c>
       <c r="C13">
-        <v>0.11440631530632819</v>
+        <v>0.1146497397188927</v>
       </c>
       <c r="D13">
-        <v>0.1219258112747079</v>
+        <v>0.1220641770510646</v>
       </c>
       <c r="E13">
-        <v>0.1183609949262442</v>
+        <v>0.1178339939786226</v>
       </c>
       <c r="F13">
-        <v>0.1208954473764008</v>
+        <v>0.1206959848063127</v>
       </c>
       <c r="G13">
-        <v>0.1207531858912988</v>
+        <v>0.1201374393495269</v>
       </c>
       <c r="H13">
-        <v>0.11325473186351891</v>
+        <v>0.1123553649780053</v>
       </c>
       <c r="I13">
-        <v>0.1126633825492529</v>
+        <v>0.1121188895364498</v>
       </c>
       <c r="J13">
-        <v>0.1098940906433389</v>
+        <v>0.109250621561389</v>
       </c>
       <c r="K13">
-        <v>0.1048215022705897</v>
+        <v>0.104982227788281</v>
       </c>
       <c r="L13">
-        <v>0.10008238476912561</v>
+        <v>0.1000820686410758</v>
       </c>
       <c r="M13">
-        <v>9.9350275383133652E-2</v>
+        <v>0.09951019038676476</v>
       </c>
       <c r="N13">
-        <v>9.7465260912756563E-2</v>
+        <v>0.09804455430394714</v>
       </c>
       <c r="O13">
-        <v>9.72848521613211E-2</v>
+        <v>0.09766106511851448</v>
       </c>
       <c r="P13">
-        <v>9.5959843745842363E-2</v>
+        <v>0.09654921225128471</v>
       </c>
       <c r="Q13">
-        <v>9.6703940962184071E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.09699121621489777</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>9.8251664353223134E-2</v>
+        <v>0.09832897330351018</v>
       </c>
       <c r="C14">
-        <v>0.11455378702015891</v>
+        <v>0.1145985723973141</v>
       </c>
       <c r="D14">
-        <v>0.1157391482638102</v>
+        <v>0.1157839546553528</v>
       </c>
       <c r="E14">
-        <v>0.11919096386765431</v>
+        <v>0.1193022338305206</v>
       </c>
       <c r="F14">
-        <v>0.1200272091857255</v>
+        <v>0.1201870206567432</v>
       </c>
       <c r="G14">
-        <v>0.12295669329165559</v>
+        <v>0.1235314530640766</v>
       </c>
       <c r="H14">
-        <v>0.12076264979664419</v>
+        <v>0.121006869383405</v>
       </c>
       <c r="I14">
-        <v>0.1147652574849047</v>
+        <v>0.1154767797286884</v>
       </c>
       <c r="J14">
-        <v>0.1101431340505676</v>
+        <v>0.1103645337276024</v>
       </c>
       <c r="K14">
-        <v>0.1085698782537209</v>
+        <v>0.1092793946425171</v>
       </c>
       <c r="L14">
-        <v>0.1071848509800509</v>
+        <v>0.1074919584130512</v>
       </c>
       <c r="M14">
-        <v>0.10093683672423361</v>
+        <v>0.1012022602192773</v>
       </c>
       <c r="N14">
-        <v>9.3615503934523253E-2</v>
+        <v>0.09387695055437624</v>
       </c>
       <c r="O14">
-        <v>9.1159233344896506E-2</v>
+        <v>0.09162326996667577</v>
       </c>
       <c r="P14">
-        <v>8.8896631383541994E-2</v>
+        <v>0.08962604189544392</v>
       </c>
       <c r="Q14">
-        <v>8.7450619202832286E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.08780906426552086</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.10301010867703091</v>
+        <v>0.1021894740604738</v>
       </c>
       <c r="C15">
-        <v>0.1146650359790031</v>
+        <v>0.1147969043620214</v>
       </c>
       <c r="D15">
-        <v>0.1158233159500712</v>
+        <v>0.1159950275213867</v>
       </c>
       <c r="E15">
-        <v>0.1194354848122107</v>
+        <v>0.1194674141565047</v>
       </c>
       <c r="F15">
-        <v>0.12027126191208851</v>
+        <v>0.1202963228792437</v>
       </c>
       <c r="G15">
-        <v>0.12354097375035571</v>
+        <v>0.1236396897874191</v>
       </c>
       <c r="H15">
-        <v>0.121090336106201</v>
+        <v>0.1213939713429814</v>
       </c>
       <c r="I15">
-        <v>0.11554330118631929</v>
+        <v>0.1154550731523937</v>
       </c>
       <c r="J15">
-        <v>0.11125811471492821</v>
+        <v>0.1114146341693586</v>
       </c>
       <c r="K15">
-        <v>0.1094079064781011</v>
+        <v>0.1098954880309775</v>
       </c>
       <c r="L15">
-        <v>0.108464558238329</v>
+        <v>0.1081489880354842</v>
       </c>
       <c r="M15">
-        <v>0.1030317611890085</v>
+        <v>0.1024993754235933</v>
       </c>
       <c r="N15">
-        <v>9.5958311778605809E-2</v>
+        <v>0.09601307801335729</v>
       </c>
       <c r="O15">
-        <v>9.3182544068423023E-2</v>
+        <v>0.09333309630068137</v>
       </c>
       <c r="P15">
-        <v>9.1278971337206624E-2</v>
+        <v>0.09178728915866718</v>
       </c>
       <c r="Q15">
-        <v>9.0062908241663783E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.09015518534974173</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.1015721125558377</v>
+        <v>0.1025780707810788</v>
       </c>
       <c r="C16">
-        <v>0.1143856393615998</v>
+        <v>0.114399253373649</v>
       </c>
       <c r="D16">
-        <v>0.1156913365002271</v>
+        <v>0.1156126076037557</v>
       </c>
       <c r="E16">
-        <v>0.1194104512022108</v>
+        <v>0.1191461334149716</v>
       </c>
       <c r="F16">
-        <v>0.1206379305010839</v>
+        <v>0.1199319548343521</v>
       </c>
       <c r="G16">
-        <v>0.123875461002817</v>
+        <v>0.1229027653826355</v>
       </c>
       <c r="H16">
-        <v>0.12180182963283299</v>
+        <v>0.1211944882699032</v>
       </c>
       <c r="I16">
-        <v>0.11598121227500729</v>
+        <v>0.1159539789961084</v>
       </c>
       <c r="J16">
-        <v>0.11170419488711771</v>
+        <v>0.110982377283554</v>
       </c>
       <c r="K16">
-        <v>0.11014199130323631</v>
+        <v>0.109214430587205</v>
       </c>
       <c r="L16">
-        <v>0.1091250362950206</v>
+        <v>0.1080313721122357</v>
       </c>
       <c r="M16">
-        <v>0.1034377127564774</v>
+        <v>0.102873883655276</v>
       </c>
       <c r="N16">
-        <v>9.6449325554313889E-2</v>
+        <v>0.09616980010385945</v>
       </c>
       <c r="O16">
-        <v>9.3748620266111429E-2</v>
+        <v>0.0929981846186444</v>
       </c>
       <c r="P16">
-        <v>9.1460506350281634E-2</v>
+        <v>0.09071583119901787</v>
       </c>
       <c r="Q16">
-        <v>8.9332532180013233E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.08944301034970717</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.10683619392134221</v>
+        <v>0.1055647863312677</v>
       </c>
       <c r="C17">
-        <v>0.1144313067463484</v>
+        <v>0.1144687160573252</v>
       </c>
       <c r="D17">
-        <v>0.1157721774188665</v>
+        <v>0.1158086857794122</v>
       </c>
       <c r="E17">
-        <v>0.1192838441540848</v>
+        <v>0.1194436967983081</v>
       </c>
       <c r="F17">
-        <v>0.1204852009432302</v>
+        <v>0.1203854324487635</v>
       </c>
       <c r="G17">
-        <v>0.123484413485119</v>
+        <v>0.1229620637958977</v>
       </c>
       <c r="H17">
-        <v>0.1212869760905448</v>
+        <v>0.121356844663831</v>
       </c>
       <c r="I17">
-        <v>0.1158375173223057</v>
+        <v>0.1156833326043629</v>
       </c>
       <c r="J17">
-        <v>0.1113825107640649</v>
+        <v>0.1107015390539776</v>
       </c>
       <c r="K17">
-        <v>0.1103255456878519</v>
+        <v>0.1098458433352902</v>
       </c>
       <c r="L17">
-        <v>0.1094716555031474</v>
+        <v>0.1089701909563404</v>
       </c>
       <c r="M17">
-        <v>0.10460649556858199</v>
+        <v>0.1042625380539802</v>
       </c>
       <c r="N17">
-        <v>9.8312827930291835E-2</v>
+        <v>0.09787817590811525</v>
       </c>
       <c r="O17">
-        <v>9.532550126955569E-2</v>
+        <v>0.09567272765196891</v>
       </c>
       <c r="P17">
-        <v>9.2863863449575881E-2</v>
+        <v>0.09354464273074933</v>
       </c>
       <c r="Q17">
-        <v>9.1419302487275714E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.09228556010523471</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>9.3946092729635361E-2</v>
+        <v>0.09306347541575601</v>
       </c>
       <c r="C18">
-        <v>0.1139500471073516</v>
+        <v>0.113783384720047</v>
       </c>
       <c r="D18">
-        <v>0.1176254011804803</v>
+        <v>0.1180301688576798</v>
       </c>
       <c r="E18">
-        <v>0.1155153766250807</v>
+        <v>0.1150566624509778</v>
       </c>
       <c r="F18">
-        <v>0.1205498899823533</v>
+        <v>0.1207297406558863</v>
       </c>
       <c r="G18">
-        <v>0.1090644149943627</v>
+        <v>0.1083627703107927</v>
       </c>
       <c r="H18">
-        <v>0.1044264622071697</v>
+        <v>0.1037897093632704</v>
       </c>
       <c r="I18">
-        <v>9.9439734495422122E-2</v>
+        <v>0.09905524759860988</v>
       </c>
       <c r="J18">
-        <v>9.343921070327868E-2</v>
+        <v>0.09319170000056436</v>
       </c>
       <c r="K18">
-        <v>8.8889950027827971E-2</v>
+        <v>0.08880908045211544</v>
       </c>
       <c r="L18">
-        <v>8.7147755283315531E-2</v>
+        <v>0.08743005151559471</v>
       </c>
       <c r="M18">
-        <v>8.5672452947400307E-2</v>
+        <v>0.08558215859473266</v>
       </c>
       <c r="N18">
-        <v>8.5360315312153559E-2</v>
+        <v>0.08498124328153592</v>
       </c>
       <c r="O18">
-        <v>8.7074525781812434E-2</v>
+        <v>0.08703437180086908</v>
       </c>
       <c r="P18">
-        <v>8.8535052249926319E-2</v>
+        <v>0.08863730682107365</v>
       </c>
       <c r="Q18">
-        <v>8.9906563005318949E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.09012103274119386</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>9.2205162352412579E-2</v>
+        <v>0.09283043836235727</v>
       </c>
       <c r="C19">
-        <v>0.1141159410436592</v>
+        <v>0.1140164254494748</v>
       </c>
       <c r="D19">
-        <v>0.1191910890864282</v>
+        <v>0.1194596413713032</v>
       </c>
       <c r="E19">
-        <v>0.11712986003521141</v>
+        <v>0.1172275074736696</v>
       </c>
       <c r="F19">
-        <v>0.11913069515374761</v>
+        <v>0.1199083427545585</v>
       </c>
       <c r="G19">
-        <v>0.1048783352241944</v>
+        <v>0.1055033381627878</v>
       </c>
       <c r="H19">
-        <v>9.9824913774196292E-2</v>
+        <v>0.1003660114638331</v>
       </c>
       <c r="I19">
-        <v>9.5445378828968114E-2</v>
+        <v>0.09563411432334305</v>
       </c>
       <c r="J19">
-        <v>8.9942300934570577E-2</v>
+        <v>0.09020499343038692</v>
       </c>
       <c r="K19">
-        <v>8.6273006373562555E-2</v>
+        <v>0.08693601223011209</v>
       </c>
       <c r="L19">
-        <v>8.5412510564280439E-2</v>
-      </c>
-      <c r="M19" s="2">
-        <v>8.4058907185976611E-2</v>
+        <v>0.08600770840658936</v>
+      </c>
+      <c r="M19">
+        <v>0.08429857928115182</v>
       </c>
       <c r="N19">
-        <v>8.4118012368604445E-2</v>
+        <v>0.08408731737839993</v>
       </c>
       <c r="O19">
-        <v>8.5124048195938454E-2</v>
+        <v>0.08460194719593275</v>
       </c>
       <c r="P19">
-        <v>8.4644610681272131E-2</v>
+        <v>0.08447698848961942</v>
       </c>
       <c r="Q19">
-        <v>8.5298594696451402E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.08538591898533004</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>9.3626786506528004E-2</v>
+        <v>0.09443416405307038</v>
       </c>
       <c r="C20">
-        <v>0.1141410591712614</v>
+        <v>0.1139844448909556</v>
       </c>
       <c r="D20">
-        <v>0.1204581820539745</v>
+        <v>0.1198724881245658</v>
       </c>
       <c r="E20">
-        <v>0.1177710825853194</v>
+        <v>0.1178380125851615</v>
       </c>
       <c r="F20">
-        <v>0.11269612143303161</v>
+        <v>0.1129331599160732</v>
       </c>
       <c r="G20">
-        <v>0.10593646828250181</v>
+        <v>0.1066865767259285</v>
       </c>
       <c r="H20">
-        <v>0.1037323795403549</v>
+        <v>0.1052042602401826</v>
       </c>
       <c r="I20">
-        <v>9.8324424376716554E-2</v>
+        <v>0.09922271976804058</v>
       </c>
       <c r="J20">
-        <v>9.3064769830020364E-2</v>
+        <v>0.09373140908560543</v>
       </c>
       <c r="K20">
-        <v>9.0398415237413848E-2</v>
+        <v>0.0909114237206719</v>
       </c>
       <c r="L20">
-        <v>8.6938695536656327E-2</v>
+        <v>0.08780350716952046</v>
       </c>
       <c r="M20">
-        <v>8.6510175926922062E-2</v>
+        <v>0.08717059326041489</v>
       </c>
       <c r="N20">
-        <v>8.6060947824111514E-2</v>
+        <v>0.08686589906845213</v>
       </c>
       <c r="O20">
-        <v>8.3075245691547117E-2</v>
+        <v>0.08398820438710765</v>
       </c>
       <c r="P20">
-        <v>8.3054502413506065E-2</v>
+        <v>0.08394994635237761</v>
       </c>
       <c r="Q20">
-        <v>8.2797521545373842E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.08424417462376754</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.1065280051988135</v>
+        <v>0.1070449884863395</v>
       </c>
       <c r="C21">
-        <v>0.1133445886491402</v>
+        <v>0.11323690953459</v>
       </c>
       <c r="D21">
-        <v>0.1215768904889678</v>
+        <v>0.1219183173715012</v>
       </c>
       <c r="E21">
-        <v>0.1184805171666779</v>
+        <v>0.1192022452386633</v>
       </c>
       <c r="F21">
-        <v>0.11124550010380101</v>
+        <v>0.1126705852565485</v>
       </c>
       <c r="G21">
-        <v>0.1081450311777004</v>
+        <v>0.1089494081204249</v>
       </c>
       <c r="H21">
-        <v>0.1066991299299529</v>
+        <v>0.1072507965762932</v>
       </c>
       <c r="I21">
-        <v>0.1039204562331717</v>
+        <v>0.1039979160591877</v>
       </c>
       <c r="J21">
-        <v>0.1003096470517133</v>
+        <v>0.1014670638622502</v>
       </c>
       <c r="K21">
-        <v>9.655689877380623E-2</v>
+        <v>0.09645775326295276</v>
       </c>
       <c r="L21">
-        <v>9.375168470129186E-2</v>
+        <v>0.09411133798576653</v>
       </c>
       <c r="M21">
-        <v>9.2757382946057884E-2</v>
+        <v>0.09304309806331378</v>
       </c>
       <c r="N21">
-        <v>9.3965549464559914E-2</v>
+        <v>0.09411734664479664</v>
       </c>
       <c r="O21">
-        <v>9.6576388238939728E-2</v>
+        <v>0.09620022821149464</v>
       </c>
       <c r="P21">
-        <v>9.8089964792820922E-2</v>
+        <v>0.09756790855864943</v>
       </c>
       <c r="Q21">
-        <v>9.760210873188653E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.09692982300868833</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.1109847560144341</v>
+        <v>0.1105580133811998</v>
       </c>
       <c r="C22">
-        <v>0.1130521258814621</v>
+        <v>0.1132333076900078</v>
       </c>
       <c r="D22">
-        <v>0.1214799184835969</v>
+        <v>0.1217473281203832</v>
       </c>
       <c r="E22">
-        <v>0.1182270662682524</v>
+        <v>0.1188301100165474</v>
       </c>
       <c r="F22">
-        <v>0.1114825551529107</v>
+        <v>0.1114653396482749</v>
       </c>
       <c r="G22">
-        <v>0.1081320375617017</v>
+        <v>0.1083744627515188</v>
       </c>
       <c r="H22">
-        <v>0.1070337417372129</v>
+        <v>0.1072574311489863</v>
       </c>
       <c r="I22">
-        <v>0.1053464511044732</v>
+        <v>0.1055781885505936</v>
       </c>
       <c r="J22">
-        <v>0.10381506834110719</v>
+        <v>0.1044447105260737</v>
       </c>
       <c r="K22">
-        <v>9.9586684453644367E-2</v>
+        <v>0.1002591491028318</v>
       </c>
       <c r="L22">
-        <v>9.6614426776962775E-2</v>
+        <v>0.09761351961051862</v>
       </c>
       <c r="M22">
-        <v>9.6042694073507129E-2</v>
+        <v>0.09695952974079861</v>
       </c>
       <c r="N22">
-        <v>9.5673879498523032E-2</v>
+        <v>0.09665646322507472</v>
       </c>
       <c r="O22">
-        <v>9.6744946102899229E-2</v>
+        <v>0.09784934849206987</v>
       </c>
       <c r="P22">
-        <v>9.7069877537310334E-2</v>
+        <v>0.09820807809820818</v>
       </c>
       <c r="Q22">
-        <v>9.714426511398698E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.09831258428288457</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>9.7174418087915132E-2</v>
+        <v>0.09684362501270374</v>
       </c>
       <c r="C23">
-        <v>0.1140251895826838</v>
+        <v>0.1137848386257083</v>
       </c>
       <c r="D23">
-        <v>0.1200519943520222</v>
+        <v>0.1198785222170553</v>
       </c>
       <c r="E23">
-        <v>0.1143128127577229</v>
+        <v>0.1131964548751159</v>
       </c>
       <c r="F23">
-        <v>0.1076871508056722</v>
+        <v>0.107656755679181</v>
       </c>
       <c r="G23">
-        <v>9.9329695727577536E-2</v>
+        <v>0.09890860494372461</v>
       </c>
       <c r="H23">
-        <v>9.3495613889550216E-2</v>
+        <v>0.09311802979387794</v>
       </c>
       <c r="I23">
-        <v>9.1205946928088505E-2</v>
+        <v>0.0909130894316932</v>
       </c>
       <c r="J23">
-        <v>9.0059236663355968E-2</v>
+        <v>0.08970983141770532</v>
       </c>
       <c r="K23">
-        <v>8.8439775777365143E-2</v>
+        <v>0.08846085169912347</v>
       </c>
       <c r="L23">
-        <v>8.8569869004103144E-2</v>
+        <v>0.08887671051566912</v>
       </c>
       <c r="M23">
-        <v>8.8810529845137876E-2</v>
+        <v>0.08933078060253323</v>
       </c>
       <c r="N23">
-        <v>9.0103577921202979E-2</v>
+        <v>0.0904343646157708</v>
       </c>
       <c r="O23">
-        <v>9.0407920518102036E-2</v>
+        <v>0.09084556252353913</v>
       </c>
       <c r="P23">
-        <v>9.0626520723502454E-2</v>
+        <v>0.09110566352145698</v>
       </c>
       <c r="Q23">
-        <v>9.2012978823788519E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.0923103785651026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.11407515759233899</v>
+        <v>0.1140094876836566</v>
       </c>
       <c r="C24">
-        <v>0.1139703500685969</v>
+        <v>0.1139851371999889</v>
       </c>
       <c r="D24">
-        <v>0.1120409066252568</v>
+        <v>0.1120433141650615</v>
       </c>
       <c r="E24">
-        <v>0.1080952329302337</v>
+        <v>0.1085524312443316</v>
       </c>
       <c r="F24">
-        <v>0.1122148461747535</v>
+        <v>0.1126378833199163</v>
       </c>
       <c r="G24">
-        <v>0.1132408966437523</v>
+        <v>0.1135871921235466</v>
       </c>
       <c r="H24">
-        <v>0.11593522094565741</v>
+        <v>0.1165065892167323</v>
       </c>
       <c r="I24">
-        <v>0.1154274826092981</v>
+        <v>0.1159752820308477</v>
       </c>
       <c r="J24">
-        <v>0.1167394790031184</v>
+        <v>0.1174026961070225</v>
       </c>
       <c r="K24">
-        <v>0.1209034185466648</v>
+        <v>0.1214429503151345</v>
       </c>
       <c r="L24">
-        <v>0.12824712974338601</v>
+        <v>0.1287407805422352</v>
       </c>
       <c r="M24">
-        <v>0.12736317928326021</v>
+        <v>0.1283554697531625</v>
       </c>
       <c r="N24">
-        <v>0.12900710663086201</v>
+        <v>0.1300328633540684</v>
       </c>
       <c r="O24">
-        <v>0.13315152205236011</v>
+        <v>0.1344962266714149</v>
       </c>
       <c r="P24">
-        <v>0.13651004977222439</v>
+        <v>0.1378675744616263</v>
       </c>
       <c r="Q24">
-        <v>0.14208818676601939</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>0.1427333401195671</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.1206984916511938</v>
+        <v>0.1202945192818771</v>
       </c>
       <c r="C25">
-        <v>0.1206984916511938</v>
+        <v>0.1202294616762405</v>
       </c>
       <c r="D25">
-        <v>0.117799833055678</v>
+        <v>0.1173006318471522</v>
       </c>
       <c r="E25">
-        <v>0.11824153967107071</v>
+        <v>0.1178437433100141</v>
       </c>
       <c r="F25">
-        <v>0.1168154168954844</v>
+        <v>0.1166909608931947</v>
       </c>
       <c r="G25">
-        <v>0.1201807906815143</v>
+        <v>0.1194973291247244</v>
       </c>
       <c r="H25">
-        <v>0.12390060076242899</v>
+        <v>0.1230838403102879</v>
       </c>
       <c r="I25">
-        <v>0.1235390737277824</v>
+        <v>0.1230912773716061</v>
       </c>
       <c r="J25">
-        <v>0.12122830604929399</v>
+        <v>0.1209882356555728</v>
       </c>
       <c r="K25">
-        <v>0.12303987553474061</v>
+        <v>0.123113984099442</v>
       </c>
       <c r="L25">
-        <v>0.1274287855084531</v>
+        <v>0.1278477197474191</v>
       </c>
       <c r="M25">
-        <v>0.1298662291575578</v>
+        <v>0.130443396530506</v>
       </c>
       <c r="N25">
-        <v>0.1342777053665451</v>
+        <v>0.1349652666916981</v>
       </c>
       <c r="O25">
-        <v>0.13916493445826861</v>
+        <v>0.1400236219419139</v>
       </c>
       <c r="P25">
-        <v>0.14161752436551961</v>
+        <v>0.1423517129112171</v>
       </c>
       <c r="Q25">
-        <v>0.14381568258977359</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.1440512752927921</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.11483245611628121</v>
+        <v>0.1141510209517201</v>
       </c>
       <c r="C26">
-        <v>0.1155642455784904</v>
+        <v>0.1156461994051673</v>
       </c>
       <c r="D26">
-        <v>0.1138146236031882</v>
+        <v>0.1136760844099427</v>
       </c>
       <c r="E26">
-        <v>0.10915128941928449</v>
+        <v>0.1093677184622684</v>
       </c>
       <c r="F26">
-        <v>0.107954274914699</v>
+        <v>0.1081542772617803</v>
       </c>
       <c r="G26">
-        <v>0.10724609236189291</v>
+        <v>0.107371167766366</v>
       </c>
       <c r="H26">
-        <v>0.1047992818661532</v>
+        <v>0.1053030039967561</v>
       </c>
       <c r="I26">
-        <v>0.1039567211364992</v>
+        <v>0.1045036113738816</v>
       </c>
       <c r="J26">
-        <v>0.10440869553433201</v>
+        <v>0.1042617903624028</v>
       </c>
       <c r="K26">
-        <v>0.101949435022659</v>
+        <v>0.1020460250546038</v>
       </c>
       <c r="L26">
-        <v>0.1004911765756393</v>
+        <v>0.1000049033405826</v>
       </c>
       <c r="M26">
-        <v>0.102200872740457</v>
+        <v>0.1019014385355694</v>
       </c>
       <c r="N26">
-        <v>0.1011708393141894</v>
+        <v>0.1007244064888336</v>
       </c>
       <c r="O26">
-        <v>0.1020450541723586</v>
+        <v>0.1023761282105658</v>
       </c>
       <c r="P26">
-        <v>0.10397419811840471</v>
+        <v>0.1037842238733799</v>
       </c>
       <c r="Q26">
-        <v>0.10373091952169081</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>0.1037793746389153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.1151399230074498</v>
+        <v>0.1162380526263921</v>
       </c>
       <c r="C27">
-        <v>0.118596674090471</v>
+        <v>0.1183288012707334</v>
       </c>
       <c r="D27">
-        <v>0.11641972607804579</v>
+        <v>0.1162547020959093</v>
       </c>
       <c r="E27">
-        <v>0.10544156325966129</v>
+        <v>0.1054312225100755</v>
       </c>
       <c r="F27">
-        <v>0.10394870322428081</v>
+        <v>0.1047905257566658</v>
       </c>
       <c r="G27">
-        <v>0.10548747478308081</v>
+        <v>0.1056186604090916</v>
       </c>
       <c r="H27">
-        <v>0.10587816780670919</v>
+        <v>0.1059894497913257</v>
       </c>
       <c r="I27">
-        <v>0.10638429763657491</v>
+        <v>0.1064762801144467</v>
       </c>
       <c r="J27">
-        <v>0.10936738086333141</v>
+        <v>0.1087958833809497</v>
       </c>
       <c r="K27">
-        <v>0.1064466071315589</v>
+        <v>0.1061101766654289</v>
       </c>
       <c r="L27">
-        <v>0.105456636839362</v>
+        <v>0.1053483303883726</v>
       </c>
       <c r="M27">
-        <v>0.1030198113445821</v>
+        <v>0.1034267783182775</v>
       </c>
       <c r="N27">
-        <v>0.10072372110679791</v>
+        <v>0.1009790686984477</v>
       </c>
       <c r="O27">
-        <v>0.1010903999692722</v>
+        <v>0.1010320278330736</v>
       </c>
       <c r="P27">
-        <v>0.10289072714806249</v>
+        <v>0.1027882093658299</v>
       </c>
       <c r="Q27">
-        <v>0.1044051869395452</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.1038551590000858</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.112178760563519</v>
+        <v>0.1118439291180581</v>
       </c>
       <c r="C28">
-        <v>0.1154769253922827</v>
+        <v>0.1154267389388929</v>
       </c>
       <c r="D28">
-        <v>0.1181599044269753</v>
+        <v>0.1183140898411064</v>
       </c>
       <c r="E28">
-        <v>0.1213205399944192</v>
+        <v>0.1212059488290073</v>
       </c>
       <c r="F28">
-        <v>0.1190657742724414</v>
+        <v>0.1190978083717598</v>
       </c>
       <c r="G28">
-        <v>0.11792974622994409</v>
+        <v>0.1181615926650469</v>
       </c>
       <c r="H28">
-        <v>0.1152359192602266</v>
+        <v>0.1152019145052329</v>
       </c>
       <c r="I28">
-        <v>0.1180773820814664</v>
+        <v>0.1179667707088571</v>
       </c>
       <c r="J28">
-        <v>0.115012913690313</v>
+        <v>0.1146960052509891</v>
       </c>
       <c r="K28">
-        <v>0.1068938374303668</v>
+        <v>0.1075109501681348</v>
       </c>
       <c r="L28">
-        <v>0.10061370660404351</v>
+        <v>0.1003880036585729</v>
       </c>
       <c r="M28">
-        <v>9.8469153121071962E-2</v>
+        <v>0.09829045524953357</v>
       </c>
       <c r="N28">
-        <v>9.9683659226842344E-2</v>
+        <v>0.09992608071955364</v>
       </c>
       <c r="O28">
-        <v>0.1033492933511396</v>
+        <v>0.1034379751701015</v>
       </c>
       <c r="P28">
-        <v>0.1070190659597509</v>
+        <v>0.1069224063235912</v>
       </c>
       <c r="Q28">
-        <v>0.1113282836789498</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.111660925659889</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.11098093749124679</v>
+        <v>0.112182964344413</v>
       </c>
       <c r="C29">
-        <v>0.1158198298155565</v>
+        <v>0.1158967097699677</v>
       </c>
       <c r="D29">
-        <v>0.1188963183536236</v>
+        <v>0.1187973228235217</v>
       </c>
       <c r="E29">
-        <v>0.1219662434507055</v>
+        <v>0.1218626384619392</v>
       </c>
       <c r="F29">
-        <v>0.11955147370260839</v>
+        <v>0.1194540305676368</v>
       </c>
       <c r="G29">
-        <v>0.11801908103516739</v>
+        <v>0.1182420281942268</v>
       </c>
       <c r="H29">
-        <v>0.11701144238800849</v>
+        <v>0.1171705618588285</v>
       </c>
       <c r="I29">
-        <v>0.1223102721834487</v>
+        <v>0.1219360608915472</v>
       </c>
       <c r="J29">
-        <v>0.119547490846941</v>
+        <v>0.1183159999067883</v>
       </c>
       <c r="K29">
-        <v>0.1145154830579822</v>
+        <v>0.1141089444544935</v>
       </c>
       <c r="L29">
-        <v>0.10206785797102259</v>
+        <v>0.102381941819309</v>
       </c>
       <c r="M29">
-        <v>0.1006154203603188</v>
+        <v>0.1004176447862033</v>
       </c>
       <c r="N29">
-        <v>9.9460187317760504E-2</v>
+        <v>0.09914551412548529</v>
       </c>
       <c r="O29">
-        <v>0.101093923120812</v>
+        <v>0.1007898034997672</v>
       </c>
       <c r="P29">
-        <v>0.10430644257321391</v>
+        <v>0.1039370982387769</v>
       </c>
       <c r="Q29">
-        <v>0.10837333324360771</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.1077534497882049</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.1143228276711242</v>
+        <v>0.1150990755704579</v>
       </c>
       <c r="C30">
-        <v>0.1158410310465173</v>
+        <v>0.1156924776485568</v>
       </c>
       <c r="D30">
-        <v>0.119230111423235</v>
+        <v>0.118904695344818</v>
       </c>
       <c r="E30">
-        <v>0.1201913830620872</v>
+        <v>0.119578073623398</v>
       </c>
       <c r="F30">
-        <v>0.11685723480067781</v>
+        <v>0.1163869645347033</v>
       </c>
       <c r="G30">
-        <v>0.11870403880787719</v>
+        <v>0.1189013233679165</v>
       </c>
       <c r="H30">
-        <v>0.11703862164672731</v>
+        <v>0.1169439141675783</v>
       </c>
       <c r="I30">
-        <v>0.1107781166022776</v>
+        <v>0.1114245232661569</v>
       </c>
       <c r="J30">
-        <v>0.1145083543509014</v>
+        <v>0.1147518081186082</v>
       </c>
       <c r="K30">
-        <v>0.10641058589244461</v>
+        <v>0.1070024757041417</v>
       </c>
       <c r="L30">
-        <v>0.1015206239949494</v>
+        <v>0.1016515070638637</v>
       </c>
       <c r="M30">
-        <v>0.1010251588752835</v>
+        <v>0.1005785851829374</v>
       </c>
       <c r="N30">
-        <v>0.1026564900865049</v>
+        <v>0.1017663320222195</v>
       </c>
       <c r="O30">
-        <v>0.10513598345158739</v>
+        <v>0.103963627058528</v>
       </c>
       <c r="P30">
-        <v>0.10867050627784899</v>
+        <v>0.1078250105978348</v>
       </c>
       <c r="Q30">
-        <v>0.11343078065532761</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.11268611575876</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.1042686689905923</v>
+        <v>0.1036086989193432</v>
       </c>
       <c r="C31">
-        <v>0.11562441322239039</v>
+        <v>0.1157199146216567</v>
       </c>
       <c r="D31">
-        <v>0.11894371504498211</v>
+        <v>0.1192847156638752</v>
       </c>
       <c r="E31">
-        <v>0.1195821794387109</v>
+        <v>0.1200404069921582</v>
       </c>
       <c r="F31">
-        <v>0.1168003373446683</v>
+        <v>0.1169556106750421</v>
       </c>
       <c r="G31">
-        <v>0.1184408084084291</v>
+        <v>0.1187906861028112</v>
       </c>
       <c r="H31">
-        <v>0.1170608866801757</v>
+        <v>0.117385534005902</v>
       </c>
       <c r="I31">
-        <v>0.1118056513804707</v>
+        <v>0.111854489729837</v>
       </c>
       <c r="J31">
-        <v>0.11464331157806359</v>
+        <v>0.1157678520378181</v>
       </c>
       <c r="K31">
-        <v>0.1085262240629648</v>
+        <v>0.1088691004283903</v>
       </c>
       <c r="L31">
-        <v>0.10095146626170839</v>
+        <v>0.1006831379409446</v>
       </c>
       <c r="M31">
-        <v>9.7250577980644362E-2</v>
+        <v>0.09687284231019019</v>
       </c>
       <c r="N31">
-        <v>9.5086671100856487E-2</v>
+        <v>0.09454640688499742</v>
       </c>
       <c r="O31">
-        <v>9.4107662711274062E-2</v>
+        <v>0.09357248116325489</v>
       </c>
       <c r="P31">
-        <v>9.6550651745005919E-2</v>
+        <v>0.09549307174008535</v>
       </c>
       <c r="Q31">
-        <v>9.6939334222257145E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.09576321471609721</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.1079159447355649</v>
+        <v>0.1079857491041191</v>
       </c>
       <c r="C32">
-        <v>0.1157603977132715</v>
+        <v>0.115712141868659</v>
       </c>
       <c r="D32">
-        <v>0.1189889709251974</v>
+        <v>0.1185256681425094</v>
       </c>
       <c r="E32">
-        <v>0.12162817144941709</v>
+        <v>0.121436747440563</v>
       </c>
       <c r="F32">
-        <v>0.11955364103106619</v>
+        <v>0.1190737629743409</v>
       </c>
       <c r="G32">
-        <v>0.1182392226428336</v>
+        <v>0.1180450709216662</v>
       </c>
       <c r="H32">
-        <v>0.1172961055789614</v>
+        <v>0.1172374467054416</v>
       </c>
       <c r="I32">
-        <v>0.1206590021871121</v>
+        <v>0.1207386297098142</v>
       </c>
       <c r="J32">
-        <v>0.1190592006978482</v>
+        <v>0.1191295515257424</v>
       </c>
       <c r="K32">
-        <v>0.11539629932725159</v>
+        <v>0.1157391574079969</v>
       </c>
       <c r="L32">
-        <v>0.1037414021603501</v>
+        <v>0.1040716985785074</v>
       </c>
       <c r="M32">
-        <v>0.1006063215873121</v>
+        <v>0.100496888475318</v>
       </c>
       <c r="N32">
-        <v>9.881318179757588E-2</v>
+        <v>0.09866187339986264</v>
       </c>
       <c r="O32">
-        <v>9.8203347965104132E-2</v>
+        <v>0.09728873123028045</v>
       </c>
       <c r="P32">
-        <v>9.7863603799169335E-2</v>
+        <v>0.09739241772465324</v>
       </c>
       <c r="Q32">
-        <v>9.8344644458247713E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.09728509770970914</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.10547372879957211</v>
+        <v>0.1051624165606507</v>
       </c>
       <c r="C33">
-        <v>0.1158767504777421</v>
+        <v>0.1158095650188834</v>
       </c>
       <c r="D33">
-        <v>0.1189870481212566</v>
+        <v>0.1187934511595916</v>
       </c>
       <c r="E33">
-        <v>0.1218667375141867</v>
+        <v>0.1216123547131818</v>
       </c>
       <c r="F33">
-        <v>0.1194989028437138</v>
+        <v>0.1192710406002679</v>
       </c>
       <c r="G33">
-        <v>0.1181940083872334</v>
+        <v>0.1181373531826289</v>
       </c>
       <c r="H33">
-        <v>0.1171576686750216</v>
+        <v>0.1167772429822115</v>
       </c>
       <c r="I33">
-        <v>0.1209787288358678</v>
+        <v>0.1201422812660392</v>
       </c>
       <c r="J33">
-        <v>0.11891004407436891</v>
+        <v>0.1182790135749806</v>
       </c>
       <c r="K33">
-        <v>0.11551740468978459</v>
+        <v>0.1150436655784997</v>
       </c>
       <c r="L33">
-        <v>0.1034144289344192</v>
+        <v>0.1027435926916544</v>
       </c>
       <c r="M33">
-        <v>9.9963966045298794E-2</v>
+        <v>0.09957890790228215</v>
       </c>
       <c r="N33">
-        <v>9.7424383245003923E-2</v>
+        <v>0.09755586270912243</v>
       </c>
       <c r="O33">
-        <v>9.6417388992045494E-2</v>
+        <v>0.09612665651850535</v>
       </c>
       <c r="P33">
-        <v>9.5586160140007828E-2</v>
+        <v>0.09535431450386844</v>
       </c>
       <c r="Q33">
-        <v>9.5556004494922422E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.09495203207621117</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.1059095970866395</v>
+        <v>0.1052434209119582</v>
       </c>
       <c r="C34">
-        <v>0.1157031070766515</v>
+        <v>0.1155077947402629</v>
       </c>
       <c r="D34">
-        <v>0.1187671982528784</v>
+        <v>0.1184709610947524</v>
       </c>
       <c r="E34">
-        <v>0.1215392748467919</v>
+        <v>0.1214860685845777</v>
       </c>
       <c r="F34">
-        <v>0.1193269558156775</v>
+        <v>0.1192984766199852</v>
       </c>
       <c r="G34">
-        <v>0.1184553538809289</v>
+        <v>0.117848646817709</v>
       </c>
       <c r="H34">
-        <v>0.1171953619275007</v>
+        <v>0.1166856343788837</v>
       </c>
       <c r="I34">
-        <v>0.1206164273421535</v>
+        <v>0.1202327949039949</v>
       </c>
       <c r="J34">
-        <v>0.1190278918761568</v>
+        <v>0.1189124384912526</v>
       </c>
       <c r="K34">
-        <v>0.1158016407387039</v>
+        <v>0.1159183702962381</v>
       </c>
       <c r="L34">
-        <v>0.1039678667968664</v>
+        <v>0.1042390966912858</v>
       </c>
       <c r="M34">
-        <v>0.1007264294371062</v>
+        <v>0.1006259226093117</v>
       </c>
       <c r="N34">
-        <v>9.7966986172697265E-2</v>
+        <v>0.09834603418602218</v>
       </c>
       <c r="O34">
-        <v>9.7172487255476642E-2</v>
+        <v>0.0972728615711774</v>
       </c>
       <c r="P34">
-        <v>9.6231659442149856E-2</v>
+        <v>0.09621953847857383</v>
       </c>
       <c r="Q34">
-        <v>9.6103921390673072E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.09576890581275872</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.107503564580344</v>
+        <v>0.1075309586745764</v>
       </c>
       <c r="C35">
-        <v>0.1160971133280904</v>
+        <v>0.1156755190569699</v>
       </c>
       <c r="D35">
-        <v>0.1192662069773633</v>
+        <v>0.1188454893615852</v>
       </c>
       <c r="E35">
-        <v>0.12208449599197919</v>
+        <v>0.1217624422912262</v>
       </c>
       <c r="F35">
-        <v>0.1199066897806237</v>
+        <v>0.1195472632765321</v>
       </c>
       <c r="G35">
-        <v>0.1188842599321165</v>
+        <v>0.1184661806824905</v>
       </c>
       <c r="H35">
-        <v>0.1175388299162624</v>
+        <v>0.1174645873102733</v>
       </c>
       <c r="I35">
-        <v>0.12108568030923531</v>
+        <v>0.1210673408731778</v>
       </c>
       <c r="J35">
-        <v>0.1198077973929359</v>
+        <v>0.1201227865939377</v>
       </c>
       <c r="K35">
-        <v>0.1174402740772186</v>
+        <v>0.117493562061928</v>
       </c>
       <c r="L35">
-        <v>0.10607307235310801</v>
+        <v>0.1065997278345096</v>
       </c>
       <c r="M35">
-        <v>0.1023633290753954</v>
+        <v>0.1025544429524453</v>
       </c>
       <c r="N35">
-        <v>0.10004430835787589</v>
+        <v>0.1001807233941542</v>
       </c>
       <c r="O35">
-        <v>9.792642110286813E-2</v>
+        <v>0.09799335232472632</v>
       </c>
       <c r="P35">
-        <v>9.6868007953618648E-2</v>
+        <v>0.09713878249541304</v>
       </c>
       <c r="Q35">
-        <v>9.538452161043473E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.09541912979468951</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.10752467404766421</v>
+        <v>0.1086242922620971</v>
       </c>
       <c r="C36">
-        <v>0.115684451426048</v>
+        <v>0.1159040654289855</v>
       </c>
       <c r="D36">
-        <v>0.1187288400544039</v>
+        <v>0.119256868148777</v>
       </c>
       <c r="E36">
-        <v>0.1215687689241236</v>
+        <v>0.1219031602760272</v>
       </c>
       <c r="F36">
-        <v>0.1194183449298476</v>
+        <v>0.1194023712695145</v>
       </c>
       <c r="G36">
-        <v>0.1180356397780203</v>
+        <v>0.1185231364868595</v>
       </c>
       <c r="H36">
-        <v>0.1172261286688112</v>
+        <v>0.1175523780838365</v>
       </c>
       <c r="I36">
-        <v>0.12077929298847929</v>
+        <v>0.1216556668661609</v>
       </c>
       <c r="J36">
-        <v>0.11876946730596601</v>
+        <v>0.1191465706115753</v>
       </c>
       <c r="K36">
-        <v>0.11505634679683149</v>
+        <v>0.1156914654576128</v>
       </c>
       <c r="L36">
-        <v>0.1030329600672126</v>
+        <v>0.1030125024673381</v>
       </c>
       <c r="M36">
-        <v>9.9884690064048876E-2</v>
+        <v>0.1000805240202844</v>
       </c>
       <c r="N36">
-        <v>9.8234944730845611E-2</v>
+        <v>0.09759239996514288</v>
       </c>
       <c r="O36">
-        <v>9.7484590835871202E-2</v>
+        <v>0.0970544790601587</v>
       </c>
       <c r="P36">
-        <v>9.797028467145566E-2</v>
+        <v>0.0978173433834286</v>
       </c>
       <c r="Q36">
-        <v>9.9235905311535866E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.09893671451472284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.1076197848683506</v>
+        <v>0.1075207412446564</v>
       </c>
       <c r="C37">
-        <v>0.1154834693521683</v>
+        <v>0.1154936391058342</v>
       </c>
       <c r="D37">
-        <v>0.118449021603315</v>
+        <v>0.1183026110819424</v>
       </c>
       <c r="E37">
-        <v>0.1212415269840403</v>
+        <v>0.120996712499822</v>
       </c>
       <c r="F37">
-        <v>0.1191118839101989</v>
+        <v>0.1189129028450121</v>
       </c>
       <c r="G37">
-        <v>0.11798100194724941</v>
+        <v>0.1175392009936833</v>
       </c>
       <c r="H37">
-        <v>0.11674555188917179</v>
+        <v>0.116696098821001</v>
       </c>
       <c r="I37">
-        <v>0.1206405736706764</v>
+        <v>0.1201657849610731</v>
       </c>
       <c r="J37">
-        <v>0.1188420102218772</v>
+        <v>0.1184854087519595</v>
       </c>
       <c r="K37">
-        <v>0.1152948536196946</v>
+        <v>0.1152360650912509</v>
       </c>
       <c r="L37">
-        <v>0.10296294556095099</v>
+        <v>0.1028492483164959</v>
       </c>
       <c r="M37">
-        <v>0.1001725388927909</v>
+        <v>0.1000161705156483</v>
       </c>
       <c r="N37">
-        <v>9.780533124186773E-2</v>
+        <v>0.09786174740668888</v>
       </c>
       <c r="O37">
-        <v>9.775027805899883E-2</v>
+        <v>0.09764071085504462</v>
       </c>
       <c r="P37">
-        <v>9.7902737601305814E-2</v>
+        <v>0.09790689898696885</v>
       </c>
       <c r="Q37">
-        <v>9.9200537239407582E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.09910904017236241</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.10823192089230479</v>
+        <v>0.1076372714914676</v>
       </c>
       <c r="C38">
-        <v>0.11585526687261791</v>
+        <v>0.1157032202041617</v>
       </c>
       <c r="D38">
-        <v>0.11901076411667939</v>
+        <v>0.1186737013317057</v>
       </c>
       <c r="E38">
-        <v>0.1220224241708541</v>
+        <v>0.1213677576651504</v>
       </c>
       <c r="F38">
-        <v>0.1194733999785285</v>
+        <v>0.1187744849078506</v>
       </c>
       <c r="G38">
-        <v>0.1183243654108391</v>
+        <v>0.1176226809828683</v>
       </c>
       <c r="H38">
-        <v>0.1171251605431826</v>
+        <v>0.1164258675508077</v>
       </c>
       <c r="I38">
-        <v>0.12067569457841799</v>
+        <v>0.1195761091002873</v>
       </c>
       <c r="J38">
-        <v>0.11850078523374</v>
+        <v>0.1181775546797815</v>
       </c>
       <c r="K38">
-        <v>0.11532395678503921</v>
+        <v>0.114892887077763</v>
       </c>
       <c r="L38">
-        <v>0.1034259014208455</v>
+        <v>0.1031036846179422</v>
       </c>
       <c r="M38">
-        <v>0.1003675968195106</v>
+        <v>0.1001464656542669</v>
       </c>
       <c r="N38">
-        <v>9.8172990225660506E-2</v>
+        <v>0.09818707567278875</v>
       </c>
       <c r="O38">
-        <v>9.7866165761495413E-2</v>
+        <v>0.09742171941048074</v>
       </c>
       <c r="P38">
-        <v>9.7985378210796226E-2</v>
+        <v>0.09682474231175453</v>
       </c>
       <c r="Q38">
-        <v>9.8581814047034866E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.09812160466439188</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.1073582449588843</v>
+        <v>0.1080998777996954</v>
       </c>
       <c r="C39">
-        <v>0.1157324536131171</v>
+        <v>0.1158204979711369</v>
       </c>
       <c r="D39">
-        <v>0.11889512365525121</v>
+        <v>0.1189115827258922</v>
       </c>
       <c r="E39">
-        <v>0.12193102873021711</v>
+        <v>0.121639982090325</v>
       </c>
       <c r="F39">
-        <v>0.1195979405054725</v>
+        <v>0.1194317317823492</v>
       </c>
       <c r="G39">
-        <v>0.1185702874163294</v>
+        <v>0.1180019852499875</v>
       </c>
       <c r="H39">
-        <v>0.11733260382978999</v>
+        <v>0.1170899777665157</v>
       </c>
       <c r="I39">
-        <v>0.121134670270773</v>
+        <v>0.1205674761974237</v>
       </c>
       <c r="J39">
-        <v>0.11928572210304859</v>
+        <v>0.1188593812894216</v>
       </c>
       <c r="K39">
-        <v>0.1163799837260788</v>
+        <v>0.1155329324297589</v>
       </c>
       <c r="L39">
-        <v>0.104812795514397</v>
+        <v>0.1037282543458346</v>
       </c>
       <c r="M39">
-        <v>0.1015130737558724</v>
+        <v>0.1009324984177762</v>
       </c>
       <c r="N39">
-        <v>9.9518999446472842E-2</v>
+        <v>0.09862472903316871</v>
       </c>
       <c r="O39">
-        <v>9.8317744577408342E-2</v>
+        <v>0.09795676707036648</v>
       </c>
       <c r="P39">
-        <v>9.7980609998649743E-2</v>
+        <v>0.09766299370552264</v>
       </c>
       <c r="Q39">
-        <v>9.8331537431650254E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.09849489385466222</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.1077531872353816</v>
+        <v>0.106702346195798</v>
       </c>
       <c r="C40">
-        <v>0.1157222004100206</v>
+        <v>0.1157957218916988</v>
       </c>
       <c r="D40">
-        <v>0.1189797878667735</v>
+        <v>0.1187063293965262</v>
       </c>
       <c r="E40">
-        <v>0.1218475473637121</v>
+        <v>0.1213163181493526</v>
       </c>
       <c r="F40">
-        <v>0.1194895811448744</v>
+        <v>0.1190708733906744</v>
       </c>
       <c r="G40">
-        <v>0.118254694830078</v>
+        <v>0.1180073286520164</v>
       </c>
       <c r="H40">
-        <v>0.1169152397400068</v>
+        <v>0.116943379477371</v>
       </c>
       <c r="I40">
-        <v>0.1197797103666305</v>
+        <v>0.1202283264284908</v>
       </c>
       <c r="J40">
-        <v>0.1185844347003901</v>
+        <v>0.1187869057334296</v>
       </c>
       <c r="K40">
-        <v>0.11585115012886341</v>
+        <v>0.1158213544461456</v>
       </c>
       <c r="L40">
-        <v>0.10556835508345699</v>
+        <v>0.1050159254101412</v>
       </c>
       <c r="M40">
-        <v>0.1017405743006852</v>
+        <v>0.1012902458999879</v>
       </c>
       <c r="N40">
-        <v>0.10040593698100581</v>
+        <v>0.09928645726414925</v>
       </c>
       <c r="O40">
-        <v>9.837049086576044E-2</v>
+        <v>0.09725120252405267</v>
       </c>
       <c r="P40">
-        <v>9.7080750957874315E-2</v>
+        <v>0.0963952832611913</v>
       </c>
       <c r="Q40">
-        <v>9.5455108136460506E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.09457998683228717</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.1196953351520417</v>
+        <v>0.1203411726060178</v>
       </c>
       <c r="C41">
-        <v>0.1180281475099992</v>
+        <v>0.1180777265140174</v>
       </c>
       <c r="D41">
-        <v>0.1212226439921375</v>
+        <v>0.1218177429455499</v>
       </c>
       <c r="E41">
-        <v>0.11761473494903769</v>
+        <v>0.1183648666451378</v>
       </c>
       <c r="F41">
-        <v>0.113393404036269</v>
+        <v>0.1136024368931457</v>
       </c>
       <c r="G41">
-        <v>0.1165467342195096</v>
+        <v>0.1168787859025793</v>
       </c>
       <c r="H41">
-        <v>0.1136665019712423</v>
+        <v>0.1140703742606337</v>
       </c>
       <c r="I41">
-        <v>0.10781499907891059</v>
+        <v>0.1086807346558239</v>
       </c>
       <c r="J41">
-        <v>0.1059183988065351</v>
+        <v>0.1065376570574061</v>
       </c>
       <c r="K41">
-        <v>0.1065679781745479</v>
+        <v>0.1068477269564636</v>
       </c>
       <c r="L41">
-        <v>0.1066954466472303</v>
+        <v>0.1063735276996065</v>
       </c>
       <c r="M41">
-        <v>0.1074520649960537</v>
+        <v>0.1073778400511941</v>
       </c>
       <c r="N41">
-        <v>0.1101955603924643</v>
+        <v>0.1097960580325194</v>
       </c>
       <c r="O41">
-        <v>0.10877887672442819</v>
+        <v>0.108545998052558</v>
       </c>
       <c r="P41">
-        <v>0.1087778402237372</v>
+        <v>0.1083721541503955</v>
       </c>
       <c r="Q41">
-        <v>0.1088935593205157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>0.1083970237198404</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.1037851462138468</v>
+        <v>0.1043731368526334</v>
       </c>
       <c r="C42">
-        <v>0.1167020074267931</v>
+        <v>0.1165643448061762</v>
       </c>
       <c r="D42">
-        <v>0.12133621587404279</v>
+        <v>0.120941320660191</v>
       </c>
       <c r="E42">
-        <v>0.1199023135798976</v>
+        <v>0.1194952659908395</v>
       </c>
       <c r="F42">
-        <v>0.1122024547621575</v>
+        <v>0.1115326654366049</v>
       </c>
       <c r="G42">
-        <v>0.11076954124526529</v>
+        <v>0.1103555201648455</v>
       </c>
       <c r="H42">
-        <v>0.103122885162722</v>
+        <v>0.1030523656388864</v>
       </c>
       <c r="I42">
-        <v>9.4763330698297552E-2</v>
+        <v>0.09566067181443408</v>
       </c>
       <c r="J42">
-        <v>9.5384662825706984E-2</v>
+        <v>0.09578398150347799</v>
       </c>
       <c r="K42">
-        <v>9.8163226789843877E-2</v>
+        <v>0.09843937907419126</v>
       </c>
       <c r="L42">
-        <v>0.1007682237873917</v>
+        <v>0.1011826412300454</v>
       </c>
       <c r="M42">
-        <v>0.10085683461963391</v>
+        <v>0.1014551828401483</v>
       </c>
       <c r="N42">
-        <v>0.101846327676894</v>
+        <v>0.1022694446896126</v>
       </c>
       <c r="O42">
-        <v>0.10078521343483419</v>
+        <v>0.1017719779877868</v>
       </c>
       <c r="P42">
-        <v>9.9711240084046929E-2</v>
+        <v>0.1005915761860742</v>
       </c>
       <c r="Q42">
-        <v>9.9129297093241087E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.09985753212969695</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.10549691886244381</v>
+        <v>0.1067686256152511</v>
       </c>
       <c r="C43">
-        <v>0.1164351308461872</v>
+        <v>0.1166488210060977</v>
       </c>
       <c r="D43">
-        <v>0.12038290735908461</v>
+        <v>0.1202677963984483</v>
       </c>
       <c r="E43">
-        <v>0.1184378871328695</v>
+        <v>0.1181804758781907</v>
       </c>
       <c r="F43">
-        <v>0.11160941280160649</v>
+        <v>0.1119656350729256</v>
       </c>
       <c r="G43">
-        <v>0.1112734465530672</v>
+        <v>0.111344816316402</v>
       </c>
       <c r="H43">
-        <v>0.10530632327808991</v>
+        <v>0.1053801603033712</v>
       </c>
       <c r="I43">
-        <v>9.7151791739091428E-2</v>
+        <v>0.09715855828241755</v>
       </c>
       <c r="J43">
-        <v>9.7690030602661473E-2</v>
+        <v>0.09767400811067799</v>
       </c>
       <c r="K43">
-        <v>9.6911551291314943E-2</v>
+        <v>0.09720079924262612</v>
       </c>
       <c r="L43">
-        <v>9.7099916023737326E-2</v>
+        <v>0.09779345705954656</v>
       </c>
       <c r="M43">
-        <v>9.8369083047886566E-2</v>
+        <v>0.09828253945431852</v>
       </c>
       <c r="N43">
-        <v>9.6797138303000366E-2</v>
+        <v>0.09724373040824913</v>
       </c>
       <c r="O43">
-        <v>9.7969744697976896E-2</v>
+        <v>0.09797302055494861</v>
       </c>
       <c r="P43">
-        <v>9.9113713788173546E-2</v>
+        <v>0.0991073520120923</v>
       </c>
       <c r="Q43">
-        <v>9.9327426564362248E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
+        <v>0.09873463963269899</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>0.1161489718797644</v>
+        <v>0.1160694160121382</v>
       </c>
       <c r="C44">
-        <v>0.1181600651012968</v>
+        <v>0.1182821548742386</v>
       </c>
       <c r="D44">
-        <v>0.1163774457626663</v>
+        <v>0.1166236874100363</v>
       </c>
       <c r="E44">
-        <v>0.1115856760787257</v>
+        <v>0.1116838435030778</v>
       </c>
       <c r="F44">
-        <v>0.11336375981567649</v>
+        <v>0.1134066400728571</v>
       </c>
       <c r="G44">
-        <v>0.1062690209625822</v>
+        <v>0.1065550195736849</v>
       </c>
       <c r="H44">
-        <v>0.1033580297010977</v>
+        <v>0.1026289176824021</v>
       </c>
       <c r="I44">
-        <v>0.1029822639306941</v>
+        <v>0.1029874396942331</v>
       </c>
       <c r="J44">
-        <v>0.10517963111538731</v>
+        <v>0.1053076596533017</v>
       </c>
       <c r="K44">
-        <v>0.1056833378563206</v>
+        <v>0.1056041755545694</v>
       </c>
       <c r="L44">
-        <v>0.10333302488921681</v>
+        <v>0.1034159334631091</v>
       </c>
       <c r="M44">
-        <v>0.1038715888641363</v>
+        <v>0.1040668456509806</v>
       </c>
       <c r="N44">
-        <v>0.1029473480867167</v>
+        <v>0.1031884197479186</v>
       </c>
       <c r="O44">
-        <v>0.10424252700230401</v>
+        <v>0.1043110924704865</v>
       </c>
       <c r="P44">
-        <v>0.1061981716353526</v>
+        <v>0.1060469353845587</v>
       </c>
       <c r="Q44">
-        <v>0.10975495010463809</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
+        <v>0.1092057866865436</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.11836380946233541</v>
+        <v>0.1184501217489029</v>
       </c>
       <c r="C45">
-        <v>0.11816532516651319</v>
+        <v>0.1182876750315514</v>
       </c>
       <c r="D45">
-        <v>0.1263026478072298</v>
+        <v>0.1270062885211053</v>
       </c>
       <c r="E45">
-        <v>0.12149841727918551</v>
+        <v>0.1219633890579051</v>
       </c>
       <c r="F45">
-        <v>0.12174044353574261</v>
+        <v>0.1216990346494259</v>
       </c>
       <c r="G45">
-        <v>0.1177043720630354</v>
+        <v>0.1178517041613216</v>
       </c>
       <c r="H45">
-        <v>0.11660628350620331</v>
+        <v>0.1166554584987256</v>
       </c>
       <c r="I45">
-        <v>0.11540549422638879</v>
+        <v>0.1155806003325335</v>
       </c>
       <c r="J45">
-        <v>0.1129065465185372</v>
+        <v>0.1130979080090069</v>
       </c>
       <c r="K45">
-        <v>0.1147741988868802</v>
+        <v>0.1145281588255732</v>
       </c>
       <c r="L45">
-        <v>0.1162654696501884</v>
+        <v>0.1162958226703595</v>
       </c>
       <c r="M45">
-        <v>0.1166573535723049</v>
+        <v>0.1160880473481839</v>
       </c>
       <c r="N45">
-        <v>0.1176616220615387</v>
+        <v>0.1172218622792674</v>
       </c>
       <c r="O45">
-        <v>0.1204671932785602</v>
+        <v>0.1200628941017145</v>
       </c>
       <c r="P45">
-        <v>0.12081786947267451</v>
+        <v>0.1205106527540746</v>
       </c>
       <c r="Q45">
-        <v>0.12153248411187439</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
+        <v>0.1215533928498523</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>0.1065703022076214</v>
+        <v>0.1064728866010351</v>
       </c>
       <c r="C46">
-        <v>0.1129754580168494</v>
+        <v>0.1130214899866195</v>
       </c>
       <c r="D46">
-        <v>0.12742788340837899</v>
+        <v>0.1275813881540055</v>
       </c>
       <c r="E46">
-        <v>0.12057627939370651</v>
+        <v>0.1207061432456829</v>
       </c>
       <c r="F46">
-        <v>0.10869186289625569</v>
+        <v>0.1080599993306307</v>
       </c>
       <c r="G46">
-        <v>0.10466654684494051</v>
+        <v>0.1042813524143531</v>
       </c>
       <c r="H46">
-        <v>0.1012763338383853</v>
+        <v>0.1015275482094735</v>
       </c>
       <c r="I46">
-        <v>9.6320720512031277E-2</v>
+        <v>0.09619074802278288</v>
       </c>
       <c r="J46">
-        <v>9.5969858215016746E-2</v>
+        <v>0.09567860856139092</v>
       </c>
       <c r="K46">
-        <v>9.6531666671243715E-2</v>
+        <v>0.09670218654371045</v>
       </c>
       <c r="L46">
-        <v>9.4826364638454064E-2</v>
+        <v>0.09529000347619011</v>
       </c>
       <c r="M46">
-        <v>9.497943238468079E-2</v>
+        <v>0.09565254871852132</v>
       </c>
       <c r="N46">
-        <v>9.631677426793428E-2</v>
+        <v>0.09700637706902809</v>
       </c>
       <c r="O46">
-        <v>9.6515024346280356E-2</v>
+        <v>0.09728686999769956</v>
       </c>
       <c r="P46">
-        <v>9.6667945587602236E-2</v>
+        <v>0.09727384599784435</v>
       </c>
       <c r="Q46">
-        <v>9.7653197615242299E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
+        <v>0.09838322184142759</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>0.10701779084667221</v>
+        <v>0.1059783452784343</v>
       </c>
       <c r="C47">
-        <v>0.11561062293544069</v>
+        <v>0.1162936509344983</v>
       </c>
       <c r="D47">
-        <v>0.11798716995166331</v>
+        <v>0.1187724020639986</v>
       </c>
       <c r="E47">
-        <v>0.1128066556031371</v>
+        <v>0.11337245401505</v>
       </c>
       <c r="F47">
-        <v>0.1106269350018274</v>
+        <v>0.1116135508120838</v>
       </c>
       <c r="G47">
-        <v>0.1018129987343247</v>
+        <v>0.1018080382300647</v>
       </c>
       <c r="H47">
-        <v>9.8313246364932078E-2</v>
+        <v>0.09885484624979202</v>
       </c>
       <c r="I47">
-        <v>9.6298192007985506E-2</v>
+        <v>0.0963308357159251</v>
       </c>
       <c r="J47">
-        <v>9.664209194453019E-2</v>
+        <v>0.09714198790465997</v>
       </c>
       <c r="K47">
-        <v>9.8802495865833825E-2</v>
+        <v>0.09916427434897306</v>
       </c>
       <c r="L47">
-        <v>9.6699475473993352E-2</v>
+        <v>0.09701201984831469</v>
       </c>
       <c r="M47">
-        <v>9.6310358115011166E-2</v>
+        <v>0.09695021996161288</v>
       </c>
       <c r="N47">
-        <v>9.6114324586856259E-2</v>
+        <v>0.096919604555956</v>
       </c>
       <c r="O47">
-        <v>9.7465930592712191E-2</v>
+        <v>0.09833670611533028</v>
       </c>
       <c r="P47">
-        <v>9.8743471721749992E-2</v>
+        <v>0.09938011854517223</v>
       </c>
       <c r="Q47">
-        <v>9.9990433959689082E-2</v>
+        <v>0.1009401394409097</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q19 C21:Q47 C20:P20">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
@@ -1,21 +1,211 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV0_RMSEP</t>
+  </si>
+  <si>
+    <t>LV1_RMSEP</t>
+  </si>
+  <si>
+    <t>LV2_RMSEP</t>
+  </si>
+  <si>
+    <t>LV3_RMSEP</t>
+  </si>
+  <si>
+    <t>LV4_RMSEP</t>
+  </si>
+  <si>
+    <t>LV5_RMSEP</t>
+  </si>
+  <si>
+    <t>LV6_RMSEP</t>
+  </si>
+  <si>
+    <t>LV7_RMSEP</t>
+  </si>
+  <si>
+    <t>LV8_RMSEP</t>
+  </si>
+  <si>
+    <t>LV9_RMSEP</t>
+  </si>
+  <si>
+    <t>LV10_RMSEP</t>
+  </si>
+  <si>
+    <t>LV11_RMSEP</t>
+  </si>
+  <si>
+    <t>LV12_RMSEP</t>
+  </si>
+  <si>
+    <t>LV13_RMSEP</t>
+  </si>
+  <si>
+    <t>LV14_RMSEP</t>
+  </si>
+  <si>
+    <t>LV15_RMSEP</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,11 +253,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +307,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +339,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +374,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2628 +550,2436 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>RMSEP_glo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_RMSEP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_RMSEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_RMSEP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_RMSEP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_RMSEP</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_RMSEP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_RMSEP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_RMSEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_RMSEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_RMSEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_RMSEP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_RMSEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_RMSEP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_RMSEP</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_RMSEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>0.1008553302131494</v>
+        <v>0.10042155466782229</v>
       </c>
       <c r="C2">
-        <v>0.1148604146349085</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D2">
-        <v>0.1170982346407076</v>
+        <v>0.11484108298228091</v>
       </c>
       <c r="E2">
-        <v>0.1169317529166724</v>
+        <v>0.11724876855100951</v>
       </c>
       <c r="F2">
-        <v>0.1160000982886547</v>
+        <v>0.1168044690109581</v>
       </c>
       <c r="G2">
-        <v>0.116987748319196</v>
+        <v>0.11573611568839939</v>
       </c>
       <c r="H2">
-        <v>0.117251423560506</v>
+        <v>0.11698765909947451</v>
       </c>
       <c r="I2">
-        <v>0.1139004428754559</v>
+        <v>0.1168909907370468</v>
       </c>
       <c r="J2">
-        <v>0.1106991700098848</v>
+        <v>0.1136493638034104</v>
       </c>
       <c r="K2">
-        <v>0.1127464869054649</v>
+        <v>0.11052387995498859</v>
       </c>
       <c r="L2">
-        <v>0.1102562623746369</v>
+        <v>0.1120788649414871</v>
       </c>
       <c r="M2">
-        <v>0.1054083757277418</v>
+        <v>0.1095974115368132</v>
       </c>
       <c r="N2">
-        <v>0.1035771817704613</v>
+        <v>0.1048061649332418</v>
       </c>
       <c r="O2">
-        <v>0.09684953339418387</v>
+        <v>0.10330370330220991</v>
       </c>
       <c r="P2">
-        <v>0.09105120627700392</v>
+        <v>9.6770166528576923E-2</v>
       </c>
       <c r="Q2">
-        <v>0.08816649166567267</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.0623601421005021E-2</v>
+      </c>
+      <c r="R2">
+        <v>8.7997932286218411E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>0.1046889852578794</v>
+        <v>0.1049236330943176</v>
       </c>
       <c r="C3">
-        <v>0.1132405395908314</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D3">
-        <v>0.1226386180505925</v>
+        <v>0.1133398249411089</v>
       </c>
       <c r="E3">
-        <v>0.1191524089712133</v>
+        <v>0.12300763422809601</v>
       </c>
       <c r="F3">
-        <v>0.111249982395368</v>
+        <v>0.1196634870401594</v>
       </c>
       <c r="G3">
-        <v>0.1063620934834092</v>
+        <v>0.11140821303327859</v>
       </c>
       <c r="H3">
-        <v>0.1031517924539951</v>
+        <v>0.106224048194899</v>
       </c>
       <c r="I3">
-        <v>0.09965434767678219</v>
+        <v>0.10332345569424969</v>
       </c>
       <c r="J3">
-        <v>0.09812185646522047</v>
+        <v>9.9820884347234351E-2</v>
       </c>
       <c r="K3">
-        <v>0.0951237808269354</v>
+        <v>9.7957666655196243E-2</v>
       </c>
       <c r="L3">
-        <v>0.09301315210451752</v>
+        <v>9.4872972318038928E-2</v>
       </c>
       <c r="M3">
-        <v>0.09331185467844615</v>
+        <v>9.2931433396290702E-2</v>
       </c>
       <c r="N3">
-        <v>0.09356379714924005</v>
+        <v>9.3460692518769845E-2</v>
       </c>
       <c r="O3">
-        <v>0.09545159901650838</v>
+        <v>9.3904018255557359E-2</v>
       </c>
       <c r="P3">
-        <v>0.09609359084632343</v>
+        <v>9.5337465209923214E-2</v>
       </c>
       <c r="Q3">
-        <v>0.09494617393796725</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>9.6337981897531136E-2</v>
+      </c>
+      <c r="R3">
+        <v>9.4931751009276588E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>0.1072362495134301</v>
+        <v>0.1086824012916955</v>
       </c>
       <c r="C4">
-        <v>0.1143122190390259</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D4">
-        <v>0.1153076252588807</v>
+        <v>0.1144500091021714</v>
       </c>
       <c r="E4">
-        <v>0.1193045173305053</v>
+        <v>0.1156640107733545</v>
       </c>
       <c r="F4">
-        <v>0.1191354603808063</v>
+        <v>0.1195751674801086</v>
       </c>
       <c r="G4">
-        <v>0.1221183466730168</v>
+        <v>0.120012703058266</v>
       </c>
       <c r="H4">
-        <v>0.1164489693260793</v>
+        <v>0.1230883008176038</v>
       </c>
       <c r="I4">
-        <v>0.1111712165036118</v>
+        <v>0.1163785161806828</v>
       </c>
       <c r="J4">
-        <v>0.108547895250518</v>
+        <v>0.11188613585363449</v>
       </c>
       <c r="K4">
-        <v>0.1084885269668619</v>
+        <v>0.109321581508787</v>
       </c>
       <c r="L4">
-        <v>0.1044487595234194</v>
+        <v>0.1087070065833733</v>
       </c>
       <c r="M4">
-        <v>0.09984785201819911</v>
+        <v>0.10466438214059059</v>
       </c>
       <c r="N4">
-        <v>0.09568982722875033</v>
+        <v>0.1000562579620811</v>
       </c>
       <c r="O4">
-        <v>0.09355851113328763</v>
+        <v>9.6309745465086041E-2</v>
       </c>
       <c r="P4">
-        <v>0.09330209288631988</v>
+        <v>9.3958124516427904E-2</v>
       </c>
       <c r="Q4">
-        <v>0.09437705407006808</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.3897585513068871E-2</v>
+      </c>
+      <c r="R4">
+        <v>9.4981676984736044E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>0.09802731676055335</v>
+        <v>9.7454870012573844E-2</v>
       </c>
       <c r="C5">
-        <v>0.1137771338278501</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D5">
-        <v>0.117817984162642</v>
+        <v>0.1139449002160591</v>
       </c>
       <c r="E5">
-        <v>0.1149281393249069</v>
+        <v>0.117575797133684</v>
       </c>
       <c r="F5">
-        <v>0.1201881694516398</v>
+        <v>0.1148997548091346</v>
       </c>
       <c r="G5">
-        <v>0.1093553314730501</v>
+        <v>0.1198370462403502</v>
       </c>
       <c r="H5">
-        <v>0.1037656995695686</v>
+        <v>0.1092826573667199</v>
       </c>
       <c r="I5">
-        <v>0.1019911391760397</v>
+        <v>0.1040377515939412</v>
       </c>
       <c r="J5">
-        <v>0.09732361754928549</v>
+        <v>0.10125688974330101</v>
       </c>
       <c r="K5">
-        <v>0.09239635594200374</v>
+        <v>9.6705727373325903E-2</v>
       </c>
       <c r="L5">
-        <v>0.09027850230263419</v>
+        <v>9.1890001675358254E-2</v>
       </c>
       <c r="M5">
-        <v>0.08835624352805323</v>
+        <v>8.9917617731852487E-2</v>
       </c>
       <c r="N5">
-        <v>0.08858376222229541</v>
+        <v>8.771408672123375E-2</v>
       </c>
       <c r="O5">
-        <v>0.09051240722079215</v>
+        <v>8.7580398047972116E-2</v>
       </c>
       <c r="P5">
-        <v>0.09203276478502925</v>
+        <v>8.9431784850402707E-2</v>
       </c>
       <c r="Q5">
-        <v>0.09368309776316465</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>9.0575984371270415E-2</v>
+      </c>
+      <c r="R5">
+        <v>9.2280463374823235E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>0.09337746042849331</v>
+        <v>9.4657166256619962E-2</v>
       </c>
       <c r="C6">
-        <v>0.1142218325778378</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D6">
-        <v>0.1187731307719691</v>
+        <v>0.11405518313136991</v>
       </c>
       <c r="E6">
-        <v>0.1160263344959161</v>
+        <v>0.1188971406618423</v>
       </c>
       <c r="F6">
-        <v>0.1176719096807987</v>
+        <v>0.116364387223456</v>
       </c>
       <c r="G6">
-        <v>0.1048595597549985</v>
+        <v>0.1180791143418659</v>
       </c>
       <c r="H6">
-        <v>0.09907313787045703</v>
+        <v>0.1057425307156427</v>
       </c>
       <c r="I6">
-        <v>0.09529597331330948</v>
+        <v>9.9460182058731542E-2</v>
       </c>
       <c r="J6">
-        <v>0.09049668198820184</v>
+        <v>9.6085245585163084E-2</v>
       </c>
       <c r="K6">
-        <v>0.0875303651310365</v>
+        <v>9.0578905325327808E-2</v>
       </c>
       <c r="L6">
-        <v>0.08640637609268483</v>
+        <v>8.7856955532271297E-2</v>
       </c>
       <c r="M6">
-        <v>0.08492586891853143</v>
+        <v>8.7078461890235256E-2</v>
       </c>
       <c r="N6">
-        <v>0.08496816369416786</v>
+        <v>8.5591172214724814E-2</v>
       </c>
       <c r="O6">
-        <v>0.08561891835141473</v>
+        <v>8.5081123001868597E-2</v>
       </c>
       <c r="P6">
-        <v>0.08534467109291174</v>
+        <v>8.5854671101381924E-2</v>
       </c>
       <c r="Q6">
-        <v>0.08677607252043083</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>8.5357327405283595E-2</v>
+      </c>
+      <c r="R6">
+        <v>8.6939855015819217E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>0.1064714022795334</v>
+        <v>0.10610403784969639</v>
       </c>
       <c r="C7">
-        <v>0.1146523710394368</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D7">
-        <v>0.1159857369623651</v>
+        <v>0.1144962419327282</v>
       </c>
       <c r="E7">
-        <v>0.1196115401185697</v>
+        <v>0.1157670103724374</v>
       </c>
       <c r="F7">
-        <v>0.1209090527164597</v>
+        <v>0.1193677731041393</v>
       </c>
       <c r="G7">
-        <v>0.1241201407997516</v>
+        <v>0.1206275461530391</v>
       </c>
       <c r="H7">
-        <v>0.1217342512298871</v>
+        <v>0.12423887743746009</v>
       </c>
       <c r="I7">
-        <v>0.1152804906214999</v>
+        <v>0.12138098248148731</v>
       </c>
       <c r="J7">
-        <v>0.1101714141491665</v>
+        <v>0.1154992983915641</v>
       </c>
       <c r="K7">
-        <v>0.1085314306155861</v>
+        <v>0.1100747780105093</v>
       </c>
       <c r="L7">
-        <v>0.1075095049985089</v>
+        <v>0.1085497832628402</v>
       </c>
       <c r="M7">
-        <v>0.1021525334426141</v>
+        <v>0.1077991316773543</v>
       </c>
       <c r="N7">
-        <v>0.09742549030221814</v>
+        <v>0.1014971063465777</v>
       </c>
       <c r="O7">
-        <v>0.09417967207526218</v>
+        <v>9.6999284414264669E-2</v>
       </c>
       <c r="P7">
-        <v>0.09226052607390395</v>
+        <v>9.321038057818358E-2</v>
       </c>
       <c r="Q7">
-        <v>0.09192515196000554</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>9.1639386975408091E-2</v>
+      </c>
+      <c r="R7">
+        <v>9.135982499410443E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>0.1026903328296165</v>
+        <v>0.10166208199045949</v>
       </c>
       <c r="C8">
-        <v>0.1142447188674363</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D8">
-        <v>0.1158193611373985</v>
+        <v>0.1143002829336638</v>
       </c>
       <c r="E8">
-        <v>0.1195905055557177</v>
+        <v>0.11596736453590049</v>
       </c>
       <c r="F8">
-        <v>0.1217796573240957</v>
+        <v>0.1198213405870186</v>
       </c>
       <c r="G8">
-        <v>0.1182598618590907</v>
+        <v>0.1223796919127469</v>
       </c>
       <c r="H8">
-        <v>0.1125589859569435</v>
+        <v>0.1188043765115096</v>
       </c>
       <c r="I8">
-        <v>0.1117627666731298</v>
+        <v>0.1129748587966032</v>
       </c>
       <c r="J8">
-        <v>0.1057672021856223</v>
+        <v>0.1120276568542295</v>
       </c>
       <c r="K8">
-        <v>0.1034922956126765</v>
+        <v>0.1059902726669332</v>
       </c>
       <c r="L8">
-        <v>0.09591984596272006</v>
+        <v>0.1032553697056524</v>
       </c>
       <c r="M8">
-        <v>0.09457566258930843</v>
+        <v>9.596342650670843E-2</v>
       </c>
       <c r="N8">
-        <v>0.09151310381792929</v>
+        <v>9.4841323617117612E-2</v>
       </c>
       <c r="O8">
-        <v>0.0898381597586549</v>
+        <v>9.2035935131598037E-2</v>
       </c>
       <c r="P8">
-        <v>0.08982931530329619</v>
+        <v>9.0366169698863852E-2</v>
       </c>
       <c r="Q8">
-        <v>0.09102746654555567</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>9.039175894888403E-2</v>
+      </c>
+      <c r="R8">
+        <v>9.122571097172999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>0.09784703362082237</v>
+        <v>9.8235914835941615E-2</v>
       </c>
       <c r="C9">
-        <v>0.1139401661812223</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D9">
-        <v>0.115581047819384</v>
+        <v>0.11411639661733521</v>
       </c>
       <c r="E9">
-        <v>0.1191967450099261</v>
+        <v>0.1154128155202583</v>
       </c>
       <c r="F9">
-        <v>0.1204414279659199</v>
+        <v>0.1190387391063658</v>
       </c>
       <c r="G9">
-        <v>0.1178147596679511</v>
+        <v>0.120654580389187</v>
       </c>
       <c r="H9">
-        <v>0.1120573715190038</v>
+        <v>0.1180242811916562</v>
       </c>
       <c r="I9">
-        <v>0.1112034872923437</v>
+        <v>0.1123521177473417</v>
       </c>
       <c r="J9">
-        <v>0.1055007380943934</v>
+        <v>0.111678235876799</v>
       </c>
       <c r="K9">
-        <v>0.1036533682937286</v>
+        <v>0.1058723264493525</v>
       </c>
       <c r="L9">
-        <v>0.09394670086247843</v>
+        <v>0.1040930828560801</v>
       </c>
       <c r="M9">
-        <v>0.09418274530936577</v>
+        <v>9.4302858931938807E-2</v>
       </c>
       <c r="N9">
-        <v>0.09116753304325097</v>
+        <v>9.483776903281553E-2</v>
       </c>
       <c r="O9">
-        <v>0.0891495471975343</v>
+        <v>9.175947879894579E-2</v>
       </c>
       <c r="P9">
-        <v>0.08961729606372015</v>
+        <v>8.9812415878787744E-2</v>
       </c>
       <c r="Q9">
-        <v>0.08969607854386755</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>9.0087417861404007E-2</v>
+      </c>
+      <c r="R9">
+        <v>9.0212072387738221E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>0.09965230724602493</v>
+        <v>9.9698459232406278E-2</v>
       </c>
       <c r="C10">
-        <v>0.1143951684038228</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D10">
-        <v>0.1157742410266587</v>
+        <v>0.1142534587394905</v>
       </c>
       <c r="E10">
-        <v>0.1192917647814444</v>
+        <v>0.1159564535864604</v>
       </c>
       <c r="F10">
-        <v>0.1209811391446332</v>
+        <v>0.1194475039821329</v>
       </c>
       <c r="G10">
-        <v>0.1181640244835191</v>
+        <v>0.12079692872941609</v>
       </c>
       <c r="H10">
-        <v>0.1127232403465558</v>
+        <v>0.11809365172186061</v>
       </c>
       <c r="I10">
-        <v>0.1114836332365461</v>
+        <v>0.11226240817421219</v>
       </c>
       <c r="J10">
-        <v>0.1061330557833374</v>
+        <v>0.1115156119120297</v>
       </c>
       <c r="K10">
-        <v>0.104520162553899</v>
+        <v>0.1057761125139767</v>
       </c>
       <c r="L10">
-        <v>0.09414557968090675</v>
+        <v>0.1036696665306121</v>
       </c>
       <c r="M10">
-        <v>0.09535643733177424</v>
+        <v>9.4219295353785038E-2</v>
       </c>
       <c r="N10">
-        <v>0.09234631433074816</v>
+        <v>9.5026952018054042E-2</v>
       </c>
       <c r="O10">
-        <v>0.09009019957148538</v>
+        <v>9.2093674226497418E-2</v>
       </c>
       <c r="P10">
-        <v>0.09074325822736874</v>
+        <v>9.0280558186657381E-2</v>
       </c>
       <c r="Q10">
-        <v>0.09056572964223722</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>9.087411621643543E-2</v>
+      </c>
+      <c r="R10">
+        <v>9.1178074837877127E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>0.09812794132718636</v>
+        <v>9.9404661993708079E-2</v>
       </c>
       <c r="C11">
-        <v>0.1141392543708036</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D11">
-        <v>0.1158029066379898</v>
+        <v>0.1140840451259349</v>
       </c>
       <c r="E11">
-        <v>0.1196165947335094</v>
+        <v>0.1157009861247254</v>
       </c>
       <c r="F11">
-        <v>0.121517774959299</v>
+        <v>0.1192177622046232</v>
       </c>
       <c r="G11">
-        <v>0.1187850781913221</v>
+        <v>0.1208178538479093</v>
       </c>
       <c r="H11">
-        <v>0.1125795030429857</v>
+        <v>0.1181632298772354</v>
       </c>
       <c r="I11">
-        <v>0.1122529890821305</v>
+        <v>0.1125019846049834</v>
       </c>
       <c r="J11">
-        <v>0.1060168136027072</v>
+        <v>0.11212909575642439</v>
       </c>
       <c r="K11">
-        <v>0.1041035149728257</v>
+        <v>0.1064306745123679</v>
       </c>
       <c r="L11">
-        <v>0.0942192479157548</v>
+        <v>0.1048588097740412</v>
       </c>
       <c r="M11">
-        <v>0.09405831697586151</v>
+        <v>9.5107174200207631E-2</v>
       </c>
       <c r="N11">
-        <v>0.0912082994034835</v>
+        <v>9.4883494441357338E-2</v>
       </c>
       <c r="O11">
-        <v>0.08961341610928832</v>
+        <v>9.1768210985464102E-2</v>
       </c>
       <c r="P11">
-        <v>0.0898780228084385</v>
+        <v>8.981082295489437E-2</v>
       </c>
       <c r="Q11">
-        <v>0.09009603009540193</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.0316433317744457E-2</v>
+      </c>
+      <c r="R11">
+        <v>9.0377229342008827E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>0.09333719583756321</v>
+        <v>9.3199153917695718E-2</v>
       </c>
       <c r="C12">
-        <v>0.113859295227354</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D12">
-        <v>0.1178126044358169</v>
+        <v>0.1136448477983663</v>
       </c>
       <c r="E12">
-        <v>0.1149174101629243</v>
+        <v>0.1172949624909152</v>
       </c>
       <c r="F12">
-        <v>0.1204209362340379</v>
+        <v>0.11525066223277459</v>
       </c>
       <c r="G12">
-        <v>0.1104011934057718</v>
+        <v>0.12003393681072989</v>
       </c>
       <c r="H12">
-        <v>0.1066104734993591</v>
+        <v>0.10963976675229339</v>
       </c>
       <c r="I12">
-        <v>0.09998162384167045</v>
+        <v>0.1064724534150378</v>
       </c>
       <c r="J12">
-        <v>0.09269408900617872</v>
+        <v>9.9304450561336799E-2</v>
       </c>
       <c r="K12">
-        <v>0.08845438477035161</v>
+        <v>9.2867336725150226E-2</v>
       </c>
       <c r="L12">
-        <v>0.08627571140577991</v>
+        <v>8.8821699499248633E-2</v>
       </c>
       <c r="M12">
-        <v>0.08387739224074835</v>
+        <v>8.6914399423174762E-2</v>
       </c>
       <c r="N12">
-        <v>0.08359797540672678</v>
+        <v>8.4877461223337586E-2</v>
       </c>
       <c r="O12">
-        <v>0.08496581711531383</v>
+        <v>8.4663468961460292E-2</v>
       </c>
       <c r="P12">
-        <v>0.08660235456802311</v>
+        <v>8.6380865322010919E-2</v>
       </c>
       <c r="Q12">
-        <v>0.08903813278613341</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>8.8171534124818624E-2</v>
+      </c>
+      <c r="R12">
+        <v>9.141668267477468E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>0.1115737854198935</v>
+        <v>0.10974047750175921</v>
       </c>
       <c r="C13">
-        <v>0.1146497397188927</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D13">
-        <v>0.1220641770510646</v>
+        <v>0.1144123719477297</v>
       </c>
       <c r="E13">
-        <v>0.1178339939786226</v>
+        <v>0.1219445040754232</v>
       </c>
       <c r="F13">
-        <v>0.1206959848063127</v>
+        <v>0.118399295233555</v>
       </c>
       <c r="G13">
-        <v>0.1201374393495269</v>
+        <v>0.1211341747493207</v>
       </c>
       <c r="H13">
-        <v>0.1123553649780053</v>
+        <v>0.1206167732569472</v>
       </c>
       <c r="I13">
-        <v>0.1121188895364498</v>
+        <v>0.1124766693992077</v>
       </c>
       <c r="J13">
-        <v>0.109250621561389</v>
+        <v>0.1123611892064023</v>
       </c>
       <c r="K13">
-        <v>0.104982227788281</v>
+        <v>0.1095177727199316</v>
       </c>
       <c r="L13">
-        <v>0.1000820686410758</v>
+        <v>0.1045580728143862</v>
       </c>
       <c r="M13">
-        <v>0.09951019038676476</v>
+        <v>9.9859599512187022E-2</v>
       </c>
       <c r="N13">
-        <v>0.09804455430394714</v>
+        <v>9.9112403743264077E-2</v>
       </c>
       <c r="O13">
-        <v>0.09766106511851448</v>
+        <v>9.6936088175688911E-2</v>
       </c>
       <c r="P13">
-        <v>0.09654921225128471</v>
+        <v>9.6908434637691068E-2</v>
       </c>
       <c r="Q13">
-        <v>0.09699121621489777</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>9.5674294533854704E-2</v>
+      </c>
+      <c r="R13">
+        <v>9.6529771499738487E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>0.09832897330351018</v>
+        <v>9.7700224233111546E-2</v>
       </c>
       <c r="C14">
-        <v>0.1145985723973141</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D14">
-        <v>0.1157839546553528</v>
+        <v>0.1146224595736311</v>
       </c>
       <c r="E14">
-        <v>0.1193022338305206</v>
+        <v>0.1158347931843534</v>
       </c>
       <c r="F14">
-        <v>0.1201870206567432</v>
+        <v>0.1193149033492112</v>
       </c>
       <c r="G14">
-        <v>0.1235314530640766</v>
+        <v>0.11998830085816881</v>
       </c>
       <c r="H14">
-        <v>0.121006869383405</v>
+        <v>0.1231604069719173</v>
       </c>
       <c r="I14">
-        <v>0.1154767797286884</v>
+        <v>0.1211442643680388</v>
       </c>
       <c r="J14">
-        <v>0.1103645337276024</v>
+        <v>0.11523622189070749</v>
       </c>
       <c r="K14">
-        <v>0.1092793946425171</v>
+        <v>0.1099520222251079</v>
       </c>
       <c r="L14">
-        <v>0.1074919584130512</v>
+        <v>0.10817917436836461</v>
       </c>
       <c r="M14">
-        <v>0.1012022602192773</v>
+        <v>0.10749142188831901</v>
       </c>
       <c r="N14">
-        <v>0.09387695055437624</v>
+        <v>0.10089296952995409</v>
       </c>
       <c r="O14">
-        <v>0.09162326996667577</v>
+        <v>9.3666417404582564E-2</v>
       </c>
       <c r="P14">
-        <v>0.08962604189544392</v>
+        <v>9.077710423743332E-2</v>
       </c>
       <c r="Q14">
-        <v>0.08780906426552086</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>8.8909500939559086E-2</v>
+      </c>
+      <c r="R14">
+        <v>8.7821991168907459E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>0.1021894740604738</v>
+        <v>0.10314912552583751</v>
       </c>
       <c r="C15">
-        <v>0.1147969043620214</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D15">
-        <v>0.1159950275213867</v>
+        <v>0.1147003384509484</v>
       </c>
       <c r="E15">
-        <v>0.1194674141565047</v>
+        <v>0.1158326044294726</v>
       </c>
       <c r="F15">
-        <v>0.1202963228792437</v>
+        <v>0.1193784110528201</v>
       </c>
       <c r="G15">
-        <v>0.1236396897874191</v>
+        <v>0.1203338818756869</v>
       </c>
       <c r="H15">
-        <v>0.1213939713429814</v>
+        <v>0.12354985572639671</v>
       </c>
       <c r="I15">
-        <v>0.1154550731523937</v>
+        <v>0.1210310380404237</v>
       </c>
       <c r="J15">
-        <v>0.1114146341693586</v>
+        <v>0.1153851418683528</v>
       </c>
       <c r="K15">
-        <v>0.1098954880309775</v>
+        <v>0.11052476192600851</v>
       </c>
       <c r="L15">
-        <v>0.1081489880354842</v>
+        <v>0.1093130002007789</v>
       </c>
       <c r="M15">
-        <v>0.1024993754235933</v>
+        <v>0.108272471456017</v>
       </c>
       <c r="N15">
-        <v>0.09601307801335729</v>
+        <v>0.1024715718612156</v>
       </c>
       <c r="O15">
-        <v>0.09333309630068137</v>
+        <v>9.6409310726543254E-2</v>
       </c>
       <c r="P15">
-        <v>0.09178728915866718</v>
+        <v>9.3657531948789494E-2</v>
       </c>
       <c r="Q15">
-        <v>0.09015518534974173</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>9.184176961733323E-2</v>
+      </c>
+      <c r="R15">
+        <v>9.0611145097549736E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>0.1025780707810788</v>
+        <v>0.1024712884284865</v>
       </c>
       <c r="C16">
-        <v>0.114399253373649</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D16">
-        <v>0.1156126076037557</v>
+        <v>0.1143425285121223</v>
       </c>
       <c r="E16">
-        <v>0.1191461334149716</v>
+        <v>0.1155832477061334</v>
       </c>
       <c r="F16">
-        <v>0.1199319548343521</v>
+        <v>0.11934192532477431</v>
       </c>
       <c r="G16">
-        <v>0.1229027653826355</v>
+        <v>0.1204025645379638</v>
       </c>
       <c r="H16">
-        <v>0.1211944882699032</v>
+        <v>0.123497320283627</v>
       </c>
       <c r="I16">
-        <v>0.1159539789961084</v>
+        <v>0.1215766848053576</v>
       </c>
       <c r="J16">
-        <v>0.110982377283554</v>
+        <v>0.1158584679550085</v>
       </c>
       <c r="K16">
-        <v>0.109214430587205</v>
+        <v>0.11120004787059901</v>
       </c>
       <c r="L16">
-        <v>0.1080313721122357</v>
+        <v>0.10963941547983</v>
       </c>
       <c r="M16">
-        <v>0.102873883655276</v>
+        <v>0.1088836727094081</v>
       </c>
       <c r="N16">
-        <v>0.09616980010385945</v>
+        <v>0.1034168279880618</v>
       </c>
       <c r="O16">
-        <v>0.0929981846186444</v>
+        <v>9.6087805997768505E-2</v>
       </c>
       <c r="P16">
-        <v>0.09071583119901787</v>
+        <v>9.3635203930024113E-2</v>
       </c>
       <c r="Q16">
-        <v>0.08944301034970717</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>9.1640150230205594E-2</v>
+      </c>
+      <c r="R16">
+        <v>8.9834419317742914E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>0.1055647863312677</v>
+        <v>0.106725392999478</v>
       </c>
       <c r="C17">
-        <v>0.1144687160573252</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D17">
-        <v>0.1158086857794122</v>
+        <v>0.11456481107047441</v>
       </c>
       <c r="E17">
-        <v>0.1194436967983081</v>
+        <v>0.1158703268492646</v>
       </c>
       <c r="F17">
-        <v>0.1203854324487635</v>
+        <v>0.1193784978924543</v>
       </c>
       <c r="G17">
-        <v>0.1229620637958977</v>
+        <v>0.120249586430224</v>
       </c>
       <c r="H17">
-        <v>0.121356844663831</v>
+        <v>0.1234484202137358</v>
       </c>
       <c r="I17">
-        <v>0.1156833326043629</v>
+        <v>0.12128877888282411</v>
       </c>
       <c r="J17">
-        <v>0.1107015390539776</v>
+        <v>0.1156737647395729</v>
       </c>
       <c r="K17">
-        <v>0.1098458433352902</v>
+        <v>0.1112251743338853</v>
       </c>
       <c r="L17">
-        <v>0.1089701909563404</v>
+        <v>0.1100668177894599</v>
       </c>
       <c r="M17">
-        <v>0.1042625380539802</v>
+        <v>0.10921578392780611</v>
       </c>
       <c r="N17">
-        <v>0.09787817590811525</v>
+        <v>0.10371084271647681</v>
       </c>
       <c r="O17">
-        <v>0.09567272765196891</v>
+        <v>9.7665972301395038E-2</v>
       </c>
       <c r="P17">
-        <v>0.09354464273074933</v>
+        <v>9.5422472591888033E-2</v>
       </c>
       <c r="Q17">
-        <v>0.09228556010523471</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.3541474688390885E-2</v>
+      </c>
+      <c r="R17">
+        <v>9.1805711756656486E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>0.09306347541575601</v>
+        <v>9.3688810471094841E-2</v>
       </c>
       <c r="C18">
-        <v>0.113783384720047</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D18">
-        <v>0.1180301688576798</v>
+        <v>0.11393013322163351</v>
       </c>
       <c r="E18">
-        <v>0.1150566624509778</v>
+        <v>0.1178219777346828</v>
       </c>
       <c r="F18">
-        <v>0.1207297406558863</v>
+        <v>0.11579097691064751</v>
       </c>
       <c r="G18">
-        <v>0.1083627703107927</v>
+        <v>0.1207096478478861</v>
       </c>
       <c r="H18">
-        <v>0.1037897093632704</v>
+        <v>0.10895661903966811</v>
       </c>
       <c r="I18">
-        <v>0.09905524759860988</v>
+        <v>0.10430804540949221</v>
       </c>
       <c r="J18">
-        <v>0.09319170000056436</v>
+        <v>9.9902918614680661E-2</v>
       </c>
       <c r="K18">
-        <v>0.08880908045211544</v>
+        <v>9.3859790676440069E-2</v>
       </c>
       <c r="L18">
-        <v>0.08743005151559471</v>
+        <v>8.8944209188767276E-2</v>
       </c>
       <c r="M18">
-        <v>0.08558215859473266</v>
+        <v>8.7761069722490592E-2</v>
       </c>
       <c r="N18">
-        <v>0.08498124328153592</v>
+        <v>8.573550400489964E-2</v>
       </c>
       <c r="O18">
-        <v>0.08703437180086908</v>
+        <v>8.5716114460570952E-2</v>
       </c>
       <c r="P18">
-        <v>0.08863730682107365</v>
+        <v>8.7325087901243659E-2</v>
       </c>
       <c r="Q18">
-        <v>0.09012103274119386</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>8.9330252048484077E-2</v>
+      </c>
+      <c r="R18">
+        <v>9.0497447488615296E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>0.09283043836235727</v>
+        <v>9.2838027015925709E-2</v>
       </c>
       <c r="C19">
-        <v>0.1140164254494748</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D19">
-        <v>0.1194596413713032</v>
+        <v>0.11416146111309219</v>
       </c>
       <c r="E19">
-        <v>0.1172275074736696</v>
+        <v>0.11908212476580041</v>
       </c>
       <c r="F19">
-        <v>0.1199083427545585</v>
+        <v>0.116193810671591</v>
       </c>
       <c r="G19">
-        <v>0.1055033381627878</v>
+        <v>0.1190528825772484</v>
       </c>
       <c r="H19">
-        <v>0.1003660114638331</v>
+        <v>0.1043531550409718</v>
       </c>
       <c r="I19">
-        <v>0.09563411432334305</v>
+        <v>0.1005043452851338</v>
       </c>
       <c r="J19">
-        <v>0.09020499343038692</v>
+        <v>9.6122341517650214E-2</v>
       </c>
       <c r="K19">
-        <v>0.08693601223011209</v>
+        <v>9.061204782943906E-2</v>
       </c>
       <c r="L19">
-        <v>0.08600770840658936</v>
+        <v>8.6869815477270948E-2</v>
       </c>
       <c r="M19">
-        <v>0.08429857928115182</v>
+        <v>8.5630992762226549E-2</v>
       </c>
       <c r="N19">
-        <v>0.08408731737839993</v>
+        <v>8.384766365388642E-2</v>
       </c>
       <c r="O19">
-        <v>0.08460194719593275</v>
+        <v>8.3824924001451015E-2</v>
       </c>
       <c r="P19">
-        <v>0.08447698848961942</v>
+        <v>8.4639274584797641E-2</v>
       </c>
       <c r="Q19">
-        <v>0.08538591898533004</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>8.4411364799827221E-2</v>
+      </c>
+      <c r="R19">
+        <v>8.5261045834951976E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>0.09443416405307038</v>
+        <v>9.4059910666150659E-2</v>
       </c>
       <c r="C20">
-        <v>0.1139844448909556</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D20">
-        <v>0.1198724881245658</v>
+        <v>0.1138918688206946</v>
       </c>
       <c r="E20">
-        <v>0.1178380125851615</v>
+        <v>0.1194848873280899</v>
       </c>
       <c r="F20">
-        <v>0.1129331599160732</v>
+        <v>0.1175326821066953</v>
       </c>
       <c r="G20">
-        <v>0.1066865767259285</v>
+        <v>0.11257322762262501</v>
       </c>
       <c r="H20">
-        <v>0.1052042602401826</v>
+        <v>0.10617230775180191</v>
       </c>
       <c r="I20">
-        <v>0.09922271976804058</v>
+        <v>0.1038201102081415</v>
       </c>
       <c r="J20">
-        <v>0.09373140908560543</v>
+        <v>9.8172704485272919E-2</v>
       </c>
       <c r="K20">
-        <v>0.0909114237206719</v>
+        <v>9.2760252603511437E-2</v>
       </c>
       <c r="L20">
-        <v>0.08780350716952046</v>
+        <v>9.019151614406723E-2</v>
       </c>
       <c r="M20">
-        <v>0.08717059326041489</v>
+        <v>8.7034684204047669E-2</v>
       </c>
       <c r="N20">
-        <v>0.08686589906845213</v>
+        <v>8.6900104756157157E-2</v>
       </c>
       <c r="O20">
-        <v>0.08398820438710765</v>
+        <v>8.679184471868312E-2</v>
       </c>
       <c r="P20">
-        <v>0.08394994635237761</v>
+        <v>8.3665490232079753E-2</v>
       </c>
       <c r="Q20">
-        <v>0.08424417462376754</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>8.4066582604125417E-2</v>
+      </c>
+      <c r="R20">
+        <v>8.4314471469758595E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>0.1070449884863395</v>
+        <v>0.10681128480111619</v>
       </c>
       <c r="C21">
-        <v>0.11323690953459</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D21">
-        <v>0.1219183173715012</v>
+        <v>0.1133179409072156</v>
       </c>
       <c r="E21">
-        <v>0.1192022452386633</v>
+        <v>0.1221362301155112</v>
       </c>
       <c r="F21">
-        <v>0.1126705852565485</v>
+        <v>0.11957356152538411</v>
       </c>
       <c r="G21">
-        <v>0.1089494081204249</v>
+        <v>0.11217911766094869</v>
       </c>
       <c r="H21">
-        <v>0.1072507965762932</v>
+        <v>0.10841733302979049</v>
       </c>
       <c r="I21">
-        <v>0.1039979160591877</v>
+        <v>0.1067297726325224</v>
       </c>
       <c r="J21">
-        <v>0.1014670638622502</v>
+        <v>0.1033335145108039</v>
       </c>
       <c r="K21">
-        <v>0.09645775326295276</v>
+        <v>0.1007058414236934</v>
       </c>
       <c r="L21">
-        <v>0.09411133798576653</v>
+        <v>9.592259173858754E-2</v>
       </c>
       <c r="M21">
-        <v>0.09304309806331378</v>
+        <v>9.3582510050331122E-2</v>
       </c>
       <c r="N21">
-        <v>0.09411734664479664</v>
+        <v>9.2573528363970661E-2</v>
       </c>
       <c r="O21">
-        <v>0.09620022821149464</v>
+        <v>9.3807238648662306E-2</v>
       </c>
       <c r="P21">
-        <v>0.09756790855864943</v>
+        <v>9.6665282767824046E-2</v>
       </c>
       <c r="Q21">
-        <v>0.09692982300868833</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.797305665911657E-2</v>
+      </c>
+      <c r="R21">
+        <v>9.7002528682656436E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>0.1105580133811998</v>
+        <v>0.1098189736273104</v>
       </c>
       <c r="C22">
-        <v>0.1132333076900078</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D22">
-        <v>0.1217473281203832</v>
+        <v>0.11306385667693521</v>
       </c>
       <c r="E22">
-        <v>0.1188301100165474</v>
+        <v>0.12139496331372179</v>
       </c>
       <c r="F22">
-        <v>0.1114653396482749</v>
+        <v>0.1189725029975888</v>
       </c>
       <c r="G22">
-        <v>0.1083744627515188</v>
+        <v>0.111596368163804</v>
       </c>
       <c r="H22">
-        <v>0.1072574311489863</v>
+        <v>0.10856415439800179</v>
       </c>
       <c r="I22">
-        <v>0.1055781885505936</v>
+        <v>0.1072029241612019</v>
       </c>
       <c r="J22">
-        <v>0.1044447105260737</v>
+        <v>0.1055350878211129</v>
       </c>
       <c r="K22">
-        <v>0.1002591491028318</v>
+        <v>0.1044902264703023</v>
       </c>
       <c r="L22">
-        <v>0.09761351961051862</v>
+        <v>9.9780702396864721E-2</v>
       </c>
       <c r="M22">
-        <v>0.09695952974079861</v>
+        <v>9.7340705137301961E-2</v>
       </c>
       <c r="N22">
-        <v>0.09665646322507472</v>
+        <v>9.6238576674606988E-2</v>
       </c>
       <c r="O22">
-        <v>0.09784934849206987</v>
+        <v>9.5703984121024904E-2</v>
       </c>
       <c r="P22">
-        <v>0.09820807809820818</v>
+        <v>9.682291778846977E-2</v>
       </c>
       <c r="Q22">
-        <v>0.09831258428288457</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>9.6911477202855423E-2</v>
+      </c>
+      <c r="R22">
+        <v>9.690333797718699E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>0.09684362501270374</v>
+        <v>9.7784766900242237E-2</v>
       </c>
       <c r="C23">
-        <v>0.1137848386257083</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D23">
-        <v>0.1198785222170553</v>
+        <v>0.11421377304206271</v>
       </c>
       <c r="E23">
-        <v>0.1131964548751159</v>
+        <v>0.12020297777402569</v>
       </c>
       <c r="F23">
-        <v>0.107656755679181</v>
+        <v>0.1147223221649856</v>
       </c>
       <c r="G23">
-        <v>0.09890860494372461</v>
+        <v>0.1078905333112114</v>
       </c>
       <c r="H23">
-        <v>0.09311802979387794</v>
+        <v>9.9552098280713097E-2</v>
       </c>
       <c r="I23">
-        <v>0.0909130894316932</v>
+        <v>9.3452329973621878E-2</v>
       </c>
       <c r="J23">
-        <v>0.08970983141770532</v>
+        <v>9.1155080653853318E-2</v>
       </c>
       <c r="K23">
-        <v>0.08846085169912347</v>
+        <v>9.0272763382096388E-2</v>
       </c>
       <c r="L23">
-        <v>0.08887671051566912</v>
+        <v>8.8716447820740646E-2</v>
       </c>
       <c r="M23">
-        <v>0.08933078060253323</v>
+        <v>8.8859984517314E-2</v>
       </c>
       <c r="N23">
-        <v>0.0904343646157708</v>
+        <v>8.9490043477417666E-2</v>
       </c>
       <c r="O23">
-        <v>0.09084556252353913</v>
+        <v>9.0457707395776049E-2</v>
       </c>
       <c r="P23">
-        <v>0.09110566352145698</v>
+        <v>9.0788920260187755E-2</v>
       </c>
       <c r="Q23">
-        <v>0.0923103785651026</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>9.1021525082719407E-2</v>
+      </c>
+      <c r="R23">
+        <v>9.2534571630234361E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>0.1140094876836566</v>
+        <v>0.1120037287055218</v>
       </c>
       <c r="C24">
-        <v>0.1139851371999889</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D24">
-        <v>0.1120433141650615</v>
+        <v>0.1156299130288642</v>
       </c>
       <c r="E24">
-        <v>0.1085524312443316</v>
+        <v>0.1185210686286928</v>
       </c>
       <c r="F24">
-        <v>0.1126378833199163</v>
+        <v>0.1213181533806123</v>
       </c>
       <c r="G24">
-        <v>0.1135871921235466</v>
+        <v>0.1194497201570958</v>
       </c>
       <c r="H24">
-        <v>0.1165065892167323</v>
+        <v>0.11839305233688981</v>
       </c>
       <c r="I24">
-        <v>0.1159752820308477</v>
+        <v>0.1155106004368</v>
       </c>
       <c r="J24">
-        <v>0.1174026961070225</v>
+        <v>0.1181432614427437</v>
       </c>
       <c r="K24">
-        <v>0.1214429503151345</v>
+        <v>0.1152451168918711</v>
       </c>
       <c r="L24">
-        <v>0.1287407805422352</v>
+        <v>0.1066834724738964</v>
       </c>
       <c r="M24">
-        <v>0.1283554697531625</v>
+        <v>0.1005366133481493</v>
       </c>
       <c r="N24">
-        <v>0.1300328633540684</v>
+        <v>9.8415810672204812E-2</v>
       </c>
       <c r="O24">
-        <v>0.1344962266714149</v>
+        <v>9.9961078616776347E-2</v>
       </c>
       <c r="P24">
-        <v>0.1378675744616263</v>
+        <v>0.1037918294822175</v>
       </c>
       <c r="Q24">
-        <v>0.1427333401195671</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.1074967551493432</v>
+      </c>
+      <c r="R24">
+        <v>0.11214276710093871</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>0.1202945192818771</v>
+        <v>0.1136247487700115</v>
       </c>
       <c r="C25">
-        <v>0.1202294616762405</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D25">
-        <v>0.1173006318471522</v>
+        <v>0.11574599850638841</v>
       </c>
       <c r="E25">
-        <v>0.1178437433100141</v>
+        <v>0.1188425868344105</v>
       </c>
       <c r="F25">
-        <v>0.1166909608931947</v>
+        <v>0.12193276600167691</v>
       </c>
       <c r="G25">
-        <v>0.1194973291247244</v>
+        <v>0.1195765909148228</v>
       </c>
       <c r="H25">
-        <v>0.1230838403102879</v>
+        <v>0.1180867262221795</v>
       </c>
       <c r="I25">
-        <v>0.1230912773716061</v>
+        <v>0.11766382345992769</v>
       </c>
       <c r="J25">
-        <v>0.1209882356555728</v>
+        <v>0.12269207084804611</v>
       </c>
       <c r="K25">
-        <v>0.123113984099442</v>
+        <v>0.11906210468748959</v>
       </c>
       <c r="L25">
-        <v>0.1278477197474191</v>
+        <v>0.11472850814991151</v>
       </c>
       <c r="M25">
-        <v>0.130443396530506</v>
+        <v>0.10298828861822509</v>
       </c>
       <c r="N25">
-        <v>0.1349652666916981</v>
+        <v>0.101249788402823</v>
       </c>
       <c r="O25">
-        <v>0.1400236219419139</v>
+        <v>0.100289142524247</v>
       </c>
       <c r="P25">
-        <v>0.1423517129112171</v>
+        <v>0.1021439448808393</v>
       </c>
       <c r="Q25">
-        <v>0.1440512752927921</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1052314257486494</v>
+      </c>
+      <c r="R25">
+        <v>0.1094423836787002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>0.1141510209517201</v>
+        <v>0.11550356835000999</v>
       </c>
       <c r="C26">
-        <v>0.1156461994051673</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D26">
-        <v>0.1136760844099427</v>
+        <v>0.1157883488612346</v>
       </c>
       <c r="E26">
-        <v>0.1093677184622684</v>
+        <v>0.1194401290507603</v>
       </c>
       <c r="F26">
-        <v>0.1081542772617803</v>
+        <v>0.1199892187713784</v>
       </c>
       <c r="G26">
-        <v>0.107371167766366</v>
+        <v>0.1170122946184502</v>
       </c>
       <c r="H26">
-        <v>0.1053030039967561</v>
+        <v>0.1192303528367756</v>
       </c>
       <c r="I26">
-        <v>0.1045036113738816</v>
+        <v>0.1171508692285349</v>
       </c>
       <c r="J26">
-        <v>0.1042617903624028</v>
+        <v>0.1110211983550507</v>
       </c>
       <c r="K26">
-        <v>0.1020460250546038</v>
+        <v>0.1144978473096112</v>
       </c>
       <c r="L26">
-        <v>0.1000049033405826</v>
+        <v>0.10675445274937879</v>
       </c>
       <c r="M26">
-        <v>0.1019014385355694</v>
+        <v>0.1017406557852702</v>
       </c>
       <c r="N26">
-        <v>0.1007244064888336</v>
+        <v>0.1010059098984236</v>
       </c>
       <c r="O26">
-        <v>0.1023761282105658</v>
+        <v>0.1023296362557672</v>
       </c>
       <c r="P26">
-        <v>0.1037842238733799</v>
+        <v>0.10440055858575011</v>
       </c>
       <c r="Q26">
-        <v>0.1037793746389153</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.1081457070829724</v>
+      </c>
+      <c r="R26">
+        <v>0.1130621422524668</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>0.1162380526263921</v>
+        <v>0.1039745010901134</v>
       </c>
       <c r="C27">
-        <v>0.1183288012707334</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D27">
-        <v>0.1162547020959093</v>
+        <v>0.1157015766663142</v>
       </c>
       <c r="E27">
-        <v>0.1054312225100755</v>
+        <v>0.11855541300790171</v>
       </c>
       <c r="F27">
-        <v>0.1047905257566658</v>
+        <v>0.1191216854851618</v>
       </c>
       <c r="G27">
-        <v>0.1056186604090916</v>
+        <v>0.1160123961867186</v>
       </c>
       <c r="H27">
-        <v>0.1059894497913257</v>
+        <v>0.1178639662467065</v>
       </c>
       <c r="I27">
-        <v>0.1064762801144467</v>
+        <v>0.1161678716923978</v>
       </c>
       <c r="J27">
-        <v>0.1087958833809497</v>
+        <v>0.1110615726347299</v>
       </c>
       <c r="K27">
-        <v>0.1061101766654289</v>
+        <v>0.1138460491878146</v>
       </c>
       <c r="L27">
-        <v>0.1053483303883726</v>
+        <v>0.10790698159204699</v>
       </c>
       <c r="M27">
-        <v>0.1034267783182775</v>
+        <v>0.1002438923885586</v>
       </c>
       <c r="N27">
-        <v>0.1009790686984477</v>
+        <v>9.6280774290876614E-2</v>
       </c>
       <c r="O27">
-        <v>0.1010320278330736</v>
+        <v>9.5063480877237358E-2</v>
       </c>
       <c r="P27">
-        <v>0.1027882093658299</v>
+        <v>9.3603590012935722E-2</v>
       </c>
       <c r="Q27">
-        <v>0.1038551590000858</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>9.5296650686734527E-2</v>
+      </c>
+      <c r="R27">
+        <v>9.5884130366224257E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>0.1118439291180581</v>
+        <v>0.10704616293446979</v>
       </c>
       <c r="C28">
-        <v>0.1154267389388929</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D28">
-        <v>0.1183140898411064</v>
+        <v>0.1156704472555639</v>
       </c>
       <c r="E28">
-        <v>0.1212059488290073</v>
+        <v>0.118475134397202</v>
       </c>
       <c r="F28">
-        <v>0.1190978083717598</v>
+        <v>0.12136696924998271</v>
       </c>
       <c r="G28">
-        <v>0.1181615926650469</v>
+        <v>0.11907242414581699</v>
       </c>
       <c r="H28">
-        <v>0.1152019145052329</v>
+        <v>0.11791541258812011</v>
       </c>
       <c r="I28">
-        <v>0.1179667707088571</v>
+        <v>0.11707673716810239</v>
       </c>
       <c r="J28">
-        <v>0.1146960052509891</v>
+        <v>0.1204800415865477</v>
       </c>
       <c r="K28">
-        <v>0.1075109501681348</v>
+        <v>0.1195772565581625</v>
       </c>
       <c r="L28">
-        <v>0.1003880036585729</v>
+        <v>0.11593674072132069</v>
       </c>
       <c r="M28">
-        <v>0.09829045524953357</v>
+        <v>0.10293187172251431</v>
       </c>
       <c r="N28">
-        <v>0.09992608071955364</v>
+        <v>0.10016857285287779</v>
       </c>
       <c r="O28">
-        <v>0.1034379751701015</v>
+        <v>9.8021361926867473E-2</v>
       </c>
       <c r="P28">
-        <v>0.1069224063235912</v>
+        <v>9.7330291189149473E-2</v>
       </c>
       <c r="Q28">
-        <v>0.111660925659889</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>9.699409373809928E-2</v>
+      </c>
+      <c r="R28">
+        <v>9.7068939503392362E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>0.112182964344413</v>
+        <v>0.10344593555754091</v>
       </c>
       <c r="C29">
-        <v>0.1158967097699677</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D29">
-        <v>0.1187973228235217</v>
+        <v>0.1157487843777921</v>
       </c>
       <c r="E29">
-        <v>0.1218626384619392</v>
+        <v>0.1188815068264524</v>
       </c>
       <c r="F29">
-        <v>0.1194540305676368</v>
+        <v>0.1217492530254338</v>
       </c>
       <c r="G29">
-        <v>0.1182420281942268</v>
+        <v>0.11930985877803869</v>
       </c>
       <c r="H29">
-        <v>0.1171705618588285</v>
+        <v>0.1179508476782004</v>
       </c>
       <c r="I29">
-        <v>0.1219360608915472</v>
+        <v>0.1167681758508816</v>
       </c>
       <c r="J29">
-        <v>0.1183159999067883</v>
+        <v>0.1200610860075262</v>
       </c>
       <c r="K29">
-        <v>0.1141089444544935</v>
+        <v>0.1184049718464084</v>
       </c>
       <c r="L29">
-        <v>0.102381941819309</v>
+        <v>0.115413058722763</v>
       </c>
       <c r="M29">
-        <v>0.1004176447862033</v>
+        <v>0.1029236079239686</v>
       </c>
       <c r="N29">
-        <v>0.09914551412548529</v>
+        <v>9.9864882885764894E-2</v>
       </c>
       <c r="O29">
-        <v>0.1007898034997672</v>
+        <v>9.7480283515426577E-2</v>
       </c>
       <c r="P29">
-        <v>0.1039370982387769</v>
+        <v>9.6612135799176435E-2</v>
       </c>
       <c r="Q29">
-        <v>0.1077534497882049</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>9.5752665791023761E-2</v>
+      </c>
+      <c r="R29">
+        <v>9.5740109057876985E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>0.1150990755704579</v>
+        <v>0.1058410623941359</v>
       </c>
       <c r="C30">
-        <v>0.1156924776485568</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D30">
-        <v>0.118904695344818</v>
+        <v>0.11578220531429639</v>
       </c>
       <c r="E30">
-        <v>0.119578073623398</v>
+        <v>0.1187646629525992</v>
       </c>
       <c r="F30">
-        <v>0.1163869645347033</v>
+        <v>0.1215362419045433</v>
       </c>
       <c r="G30">
-        <v>0.1189013233679165</v>
+        <v>0.119262979862404</v>
       </c>
       <c r="H30">
-        <v>0.1169439141675783</v>
+        <v>0.1183151174919061</v>
       </c>
       <c r="I30">
-        <v>0.1114245232661569</v>
+        <v>0.1173059803822005</v>
       </c>
       <c r="J30">
-        <v>0.1147518081186082</v>
+        <v>0.12046040910388429</v>
       </c>
       <c r="K30">
-        <v>0.1070024757041417</v>
+        <v>0.1191774717370066</v>
       </c>
       <c r="L30">
-        <v>0.1016515070638637</v>
+        <v>0.1161978059338734</v>
       </c>
       <c r="M30">
-        <v>0.1005785851829374</v>
+        <v>0.10413484861780641</v>
       </c>
       <c r="N30">
-        <v>0.1017663320222195</v>
+        <v>0.10084168365648299</v>
       </c>
       <c r="O30">
-        <v>0.103963627058528</v>
+        <v>9.8837636292215258E-2</v>
       </c>
       <c r="P30">
-        <v>0.1078250105978348</v>
+        <v>9.708076569976884E-2</v>
       </c>
       <c r="Q30">
-        <v>0.11268611575876</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>9.608832253961784E-2</v>
+      </c>
+      <c r="R30">
+        <v>9.5392618476584534E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>0.1036086989193432</v>
+        <v>0.10764062632783571</v>
       </c>
       <c r="C31">
-        <v>0.1157199146216567</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D31">
-        <v>0.1192847156638752</v>
+        <v>0.11574601530416841</v>
       </c>
       <c r="E31">
-        <v>0.1200404069921582</v>
+        <v>0.1184664611999707</v>
       </c>
       <c r="F31">
-        <v>0.1169556106750421</v>
+        <v>0.1213504526876422</v>
       </c>
       <c r="G31">
-        <v>0.1187906861028112</v>
+        <v>0.1190330682582898</v>
       </c>
       <c r="H31">
-        <v>0.117385534005902</v>
+        <v>0.1179588611380927</v>
       </c>
       <c r="I31">
-        <v>0.111854489729837</v>
+        <v>0.1169260593078973</v>
       </c>
       <c r="J31">
-        <v>0.1157678520378181</v>
+        <v>0.120506901707421</v>
       </c>
       <c r="K31">
-        <v>0.1088691004283903</v>
+        <v>0.11898782571530619</v>
       </c>
       <c r="L31">
-        <v>0.1006831379409446</v>
+        <v>0.11642491446593391</v>
       </c>
       <c r="M31">
-        <v>0.09687284231019019</v>
+        <v>0.1056803874012063</v>
       </c>
       <c r="N31">
-        <v>0.09454640688499742</v>
+        <v>0.101839574151964</v>
       </c>
       <c r="O31">
-        <v>0.09357248116325489</v>
+        <v>9.9581862880923785E-2</v>
       </c>
       <c r="P31">
-        <v>0.09549307174008535</v>
+        <v>9.7782390622230236E-2</v>
       </c>
       <c r="Q31">
-        <v>0.09576321471609721</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>9.6626166636540015E-2</v>
+      </c>
+      <c r="R31">
+        <v>9.4905561950673914E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>0.1079857491041191</v>
+        <v>0.1091826531990161</v>
       </c>
       <c r="C32">
-        <v>0.115712141868659</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D32">
-        <v>0.1185256681425094</v>
+        <v>0.11562784727953559</v>
       </c>
       <c r="E32">
-        <v>0.121436747440563</v>
+        <v>0.1187639497604701</v>
       </c>
       <c r="F32">
-        <v>0.1190737629743409</v>
+        <v>0.12165419133366551</v>
       </c>
       <c r="G32">
-        <v>0.1180450709216662</v>
+        <v>0.1195121721521834</v>
       </c>
       <c r="H32">
-        <v>0.1172374467054416</v>
+        <v>0.1180794892049175</v>
       </c>
       <c r="I32">
-        <v>0.1207386297098142</v>
+        <v>0.1171008146898924</v>
       </c>
       <c r="J32">
-        <v>0.1191295515257424</v>
+        <v>0.1208578613739533</v>
       </c>
       <c r="K32">
-        <v>0.1157391574079969</v>
+        <v>0.118862369252502</v>
       </c>
       <c r="L32">
-        <v>0.1040716985785074</v>
+        <v>0.11569921663536629</v>
       </c>
       <c r="M32">
-        <v>0.100496888475318</v>
+        <v>0.10325756263202369</v>
       </c>
       <c r="N32">
-        <v>0.09866187339986264</v>
+        <v>0.10009006544157829</v>
       </c>
       <c r="O32">
-        <v>0.09728873123028045</v>
+        <v>9.8425591057009654E-2</v>
       </c>
       <c r="P32">
-        <v>0.09739241772465324</v>
+        <v>9.8317445040527418E-2</v>
       </c>
       <c r="Q32">
-        <v>0.09728509770970914</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>9.9480949122511861E-2</v>
+      </c>
+      <c r="R32">
+        <v>0.1007796734250155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>0.1051624165606507</v>
+        <v>0.1073670217604366</v>
       </c>
       <c r="C33">
-        <v>0.1158095650188834</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D33">
-        <v>0.1187934511595916</v>
+        <v>0.11559206565918689</v>
       </c>
       <c r="E33">
-        <v>0.1216123547131818</v>
+        <v>0.11849160505436671</v>
       </c>
       <c r="F33">
-        <v>0.1192710406002679</v>
+        <v>0.12133534038965541</v>
       </c>
       <c r="G33">
-        <v>0.1181373531826289</v>
+        <v>0.11890529695740359</v>
       </c>
       <c r="H33">
-        <v>0.1167772429822115</v>
+        <v>0.11770197591949939</v>
       </c>
       <c r="I33">
-        <v>0.1201422812660392</v>
+        <v>0.11672020984203491</v>
       </c>
       <c r="J33">
-        <v>0.1182790135749806</v>
+        <v>0.1206699728505682</v>
       </c>
       <c r="K33">
-        <v>0.1150436655784997</v>
+        <v>0.11858062488892231</v>
       </c>
       <c r="L33">
-        <v>0.1027435926916544</v>
+        <v>0.11522676077471949</v>
       </c>
       <c r="M33">
-        <v>0.09957890790228215</v>
+        <v>0.10292513497833231</v>
       </c>
       <c r="N33">
-        <v>0.09755586270912243</v>
+        <v>0.1003144140203629</v>
       </c>
       <c r="O33">
-        <v>0.09612665651850535</v>
+        <v>9.8221061766306544E-2</v>
       </c>
       <c r="P33">
-        <v>0.09535431450386844</v>
+        <v>9.7792960062385928E-2</v>
       </c>
       <c r="Q33">
-        <v>0.09495203207621117</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>9.8190093847988338E-2</v>
+      </c>
+      <c r="R33">
+        <v>9.9082423864482863E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>0.1052434209119582</v>
+        <v>0.1078521762026317</v>
       </c>
       <c r="C34">
-        <v>0.1155077947402629</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D34">
-        <v>0.1184709610947524</v>
+        <v>0.1155450518586061</v>
       </c>
       <c r="E34">
-        <v>0.1214860685845777</v>
+        <v>0.1186604562318522</v>
       </c>
       <c r="F34">
-        <v>0.1192984766199852</v>
+        <v>0.1215475704272104</v>
       </c>
       <c r="G34">
-        <v>0.117848646817709</v>
+        <v>0.1194873498422771</v>
       </c>
       <c r="H34">
-        <v>0.1166856343788837</v>
+        <v>0.11816224472390729</v>
       </c>
       <c r="I34">
-        <v>0.1202327949039949</v>
+        <v>0.1171730372658044</v>
       </c>
       <c r="J34">
-        <v>0.1189124384912526</v>
+        <v>0.12052087021540379</v>
       </c>
       <c r="K34">
-        <v>0.1159183702962381</v>
+        <v>0.1194590809062364</v>
       </c>
       <c r="L34">
-        <v>0.1042390966912858</v>
+        <v>0.116133579354344</v>
       </c>
       <c r="M34">
-        <v>0.1006259226093117</v>
+        <v>0.10408189426601509</v>
       </c>
       <c r="N34">
-        <v>0.09834603418602218</v>
+        <v>0.1006957230259381</v>
       </c>
       <c r="O34">
-        <v>0.0972728615711774</v>
+        <v>9.881183121716719E-2</v>
       </c>
       <c r="P34">
-        <v>0.09621953847857383</v>
+        <v>9.8030110815300539E-2</v>
       </c>
       <c r="Q34">
-        <v>0.09576890581275872</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>9.8356825790067604E-2</v>
+      </c>
+      <c r="R34">
+        <v>9.9062624830105125E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>0.1075309586745764</v>
+        <v>0.10918495610233001</v>
       </c>
       <c r="C35">
-        <v>0.1156755190569699</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D35">
-        <v>0.1188454893615852</v>
+        <v>0.115861218537987</v>
       </c>
       <c r="E35">
-        <v>0.1217624422912262</v>
+        <v>0.11920537437493391</v>
       </c>
       <c r="F35">
-        <v>0.1195472632765321</v>
+        <v>0.1219291639054421</v>
       </c>
       <c r="G35">
-        <v>0.1184661806824905</v>
+        <v>0.1196630440321973</v>
       </c>
       <c r="H35">
-        <v>0.1174645873102733</v>
+        <v>0.11851610528471861</v>
       </c>
       <c r="I35">
-        <v>0.1210673408731778</v>
+        <v>0.1176731384353801</v>
       </c>
       <c r="J35">
-        <v>0.1201227865939377</v>
+        <v>0.12117861895950829</v>
       </c>
       <c r="K35">
-        <v>0.117493562061928</v>
+        <v>0.1197554790998957</v>
       </c>
       <c r="L35">
-        <v>0.1065997278345096</v>
+        <v>0.1164652311656228</v>
       </c>
       <c r="M35">
-        <v>0.1025544429524453</v>
+        <v>0.104542462535094</v>
       </c>
       <c r="N35">
-        <v>0.1001807233941542</v>
+        <v>0.101819735745033</v>
       </c>
       <c r="O35">
-        <v>0.09799335232472632</v>
+        <v>9.9425717576739611E-2</v>
       </c>
       <c r="P35">
-        <v>0.09713878249541304</v>
+        <v>9.8250189025975709E-2</v>
       </c>
       <c r="Q35">
-        <v>0.09541912979468951</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>9.8241503402269739E-2</v>
+      </c>
+      <c r="R35">
+        <v>9.8405077946614433E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>0.1086242922620971</v>
+        <v>0.1073422484093875</v>
       </c>
       <c r="C36">
-        <v>0.1159040654289855</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D36">
-        <v>0.119256868148777</v>
+        <v>0.1155701518227038</v>
       </c>
       <c r="E36">
-        <v>0.1219031602760272</v>
+        <v>0.11876784760425491</v>
       </c>
       <c r="F36">
-        <v>0.1194023712695145</v>
+        <v>0.1215309924248964</v>
       </c>
       <c r="G36">
-        <v>0.1185231364868595</v>
+        <v>0.1189650954611452</v>
       </c>
       <c r="H36">
-        <v>0.1175523780838365</v>
+        <v>0.1179263342433271</v>
       </c>
       <c r="I36">
-        <v>0.1216556668661609</v>
+        <v>0.1169456640398952</v>
       </c>
       <c r="J36">
-        <v>0.1191465706115753</v>
+        <v>0.1194340192194757</v>
       </c>
       <c r="K36">
-        <v>0.1156914654576128</v>
+        <v>0.11830079365589841</v>
       </c>
       <c r="L36">
-        <v>0.1030125024673381</v>
+        <v>0.1154297572180001</v>
       </c>
       <c r="M36">
-        <v>0.1000805240202844</v>
+        <v>0.1061359646468301</v>
       </c>
       <c r="N36">
-        <v>0.09759239996514288</v>
+        <v>0.1016834090556195</v>
       </c>
       <c r="O36">
-        <v>0.0970544790601587</v>
+        <v>9.9564548317472051E-2</v>
       </c>
       <c r="P36">
-        <v>0.0978173433834286</v>
+        <v>9.7591029664163512E-2</v>
       </c>
       <c r="Q36">
-        <v>0.09893671451472284</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>9.7195689862874177E-2</v>
+      </c>
+      <c r="R36">
+        <v>9.5453053430557752E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>0.1075207412446564</v>
+        <v>0.11874584982919199</v>
       </c>
       <c r="C37">
-        <v>0.1154936391058342</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D37">
-        <v>0.1183026110819424</v>
+        <v>0.1180998203677147</v>
       </c>
       <c r="E37">
-        <v>0.120996712499822</v>
+        <v>0.1218185327700569</v>
       </c>
       <c r="F37">
-        <v>0.1189129028450121</v>
+        <v>0.1180895496682618</v>
       </c>
       <c r="G37">
-        <v>0.1175392009936833</v>
+        <v>0.11338390202449759</v>
       </c>
       <c r="H37">
-        <v>0.116696098821001</v>
+        <v>0.1163654024631568</v>
       </c>
       <c r="I37">
-        <v>0.1201657849610731</v>
+        <v>0.1133721756848899</v>
       </c>
       <c r="J37">
-        <v>0.1184854087519595</v>
+        <v>0.1079054103956656</v>
       </c>
       <c r="K37">
-        <v>0.1152360650912509</v>
+        <v>0.1059954594155231</v>
       </c>
       <c r="L37">
-        <v>0.1028492483164959</v>
+        <v>0.1065469897686574</v>
       </c>
       <c r="M37">
-        <v>0.1000161705156483</v>
+        <v>0.10629124404523831</v>
       </c>
       <c r="N37">
-        <v>0.09786174740668888</v>
+        <v>0.1071211947346707</v>
       </c>
       <c r="O37">
-        <v>0.09764071085504462</v>
+        <v>0.1095542780723316</v>
       </c>
       <c r="P37">
-        <v>0.09790689898696885</v>
+        <v>0.1079460829827114</v>
       </c>
       <c r="Q37">
-        <v>0.09910904017236241</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.1077413216741919</v>
+      </c>
+      <c r="R37">
+        <v>0.10757307702002419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>0.1076372714914676</v>
+        <v>0.1045468994066972</v>
       </c>
       <c r="C38">
-        <v>0.1157032202041617</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D38">
-        <v>0.1186737013317057</v>
+        <v>0.11682464697425091</v>
       </c>
       <c r="E38">
-        <v>0.1213677576651504</v>
+        <v>0.1211396444439799</v>
       </c>
       <c r="F38">
-        <v>0.1187744849078506</v>
+        <v>0.11978531949004689</v>
       </c>
       <c r="G38">
-        <v>0.1176226809828683</v>
+        <v>0.1125394688138763</v>
       </c>
       <c r="H38">
-        <v>0.1164258675508077</v>
+        <v>0.1112956264427621</v>
       </c>
       <c r="I38">
-        <v>0.1195761091002873</v>
+        <v>0.10350749646090041</v>
       </c>
       <c r="J38">
-        <v>0.1181775546797815</v>
+        <v>9.5120795828348093E-2</v>
       </c>
       <c r="K38">
-        <v>0.114892887077763</v>
+        <v>9.574871728724535E-2</v>
       </c>
       <c r="L38">
-        <v>0.1031036846179422</v>
+        <v>9.8524076392877441E-2</v>
       </c>
       <c r="M38">
-        <v>0.1001464656542669</v>
+        <v>0.1011461839963268</v>
       </c>
       <c r="N38">
-        <v>0.09818707567278875</v>
+        <v>0.1011190930167289</v>
       </c>
       <c r="O38">
-        <v>0.09742171941048074</v>
+        <v>0.102221307964761</v>
       </c>
       <c r="P38">
-        <v>0.09682474231175453</v>
+        <v>0.10213942751981681</v>
       </c>
       <c r="Q38">
-        <v>0.09812160466439188</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.1010159945529102</v>
+      </c>
+      <c r="R38">
+        <v>0.10015737039480729</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>0.1080998777996954</v>
+        <v>0.1059475728613256</v>
       </c>
       <c r="C39">
-        <v>0.1158204979711369</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D39">
-        <v>0.1189115827258922</v>
+        <v>0.1165182733645697</v>
       </c>
       <c r="E39">
-        <v>0.121639982090325</v>
+        <v>0.12003336752744601</v>
       </c>
       <c r="F39">
-        <v>0.1194317317823492</v>
+        <v>0.1182994571576107</v>
       </c>
       <c r="G39">
-        <v>0.1180019852499875</v>
+        <v>0.1115216733359085</v>
       </c>
       <c r="H39">
-        <v>0.1170899777665157</v>
+        <v>0.1107555241426742</v>
       </c>
       <c r="I39">
-        <v>0.1205674761974237</v>
+        <v>0.1047594519980676</v>
       </c>
       <c r="J39">
-        <v>0.1188593812894216</v>
+        <v>9.7240620973479464E-2</v>
       </c>
       <c r="K39">
-        <v>0.1155329324297589</v>
+        <v>9.7745520395281699E-2</v>
       </c>
       <c r="L39">
-        <v>0.1037282543458346</v>
+        <v>9.6894575988092979E-2</v>
       </c>
       <c r="M39">
-        <v>0.1009324984177762</v>
+        <v>9.7826663458370142E-2</v>
       </c>
       <c r="N39">
-        <v>0.09862472903316871</v>
+        <v>9.8769935805948575E-2</v>
       </c>
       <c r="O39">
-        <v>0.09795676707036648</v>
+        <v>9.7608692926869883E-2</v>
       </c>
       <c r="P39">
-        <v>0.09766299370552264</v>
+        <v>9.8473837691948771E-2</v>
       </c>
       <c r="Q39">
-        <v>0.09849489385466222</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>9.9195904475717175E-2</v>
+      </c>
+      <c r="R39">
+        <v>9.9116344157107364E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>0.106702346195798</v>
+        <v>0.1160818412173031</v>
       </c>
       <c r="C40">
-        <v>0.1157957218916988</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D40">
-        <v>0.1187063293965262</v>
+        <v>0.1182777290998735</v>
       </c>
       <c r="E40">
-        <v>0.1213163181493526</v>
+        <v>0.11642068427728119</v>
       </c>
       <c r="F40">
-        <v>0.1190708733906744</v>
+        <v>0.1121412573750228</v>
       </c>
       <c r="G40">
-        <v>0.1180073286520164</v>
+        <v>0.11374668563691261</v>
       </c>
       <c r="H40">
-        <v>0.116943379477371</v>
+        <v>0.10669928594999779</v>
       </c>
       <c r="I40">
-        <v>0.1202283264284908</v>
+        <v>0.102815419366855</v>
       </c>
       <c r="J40">
-        <v>0.1187869057334296</v>
+        <v>0.10287292521671659</v>
       </c>
       <c r="K40">
-        <v>0.1158213544461456</v>
+        <v>0.10537708314522649</v>
       </c>
       <c r="L40">
-        <v>0.1050159254101412</v>
+        <v>0.10569314450267971</v>
       </c>
       <c r="M40">
-        <v>0.1012902458999879</v>
+        <v>0.1035304458495977</v>
       </c>
       <c r="N40">
-        <v>0.09928645726414925</v>
+        <v>0.1038627399950014</v>
       </c>
       <c r="O40">
-        <v>0.09725120252405267</v>
+        <v>0.10259564760017729</v>
       </c>
       <c r="P40">
-        <v>0.0963952832611913</v>
+        <v>0.1036434102079971</v>
       </c>
       <c r="Q40">
-        <v>0.09457998683228717</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1055107194672246</v>
+      </c>
+      <c r="R40">
+        <v>0.1091213725746033</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>0.1203411726060178</v>
+        <v>0.1189648475640671</v>
       </c>
       <c r="C41">
-        <v>0.1180777265140174</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D41">
-        <v>0.1218177429455499</v>
+        <v>0.1186398046841097</v>
       </c>
       <c r="E41">
-        <v>0.1183648666451378</v>
+        <v>0.12663773178560431</v>
       </c>
       <c r="F41">
-        <v>0.1136024368931457</v>
+        <v>0.122061768227312</v>
       </c>
       <c r="G41">
-        <v>0.1168787859025793</v>
+        <v>0.12188529373600659</v>
       </c>
       <c r="H41">
-        <v>0.1140703742606337</v>
+        <v>0.11795136133670769</v>
       </c>
       <c r="I41">
-        <v>0.1086807346558239</v>
+        <v>0.1168305099499122</v>
       </c>
       <c r="J41">
-        <v>0.1065376570574061</v>
+        <v>0.11557684124793791</v>
       </c>
       <c r="K41">
-        <v>0.1068477269564636</v>
+        <v>0.1129252831884477</v>
       </c>
       <c r="L41">
-        <v>0.1063735276996065</v>
+        <v>0.1145314880787506</v>
       </c>
       <c r="M41">
-        <v>0.1073778400511941</v>
+        <v>0.1164885176886227</v>
       </c>
       <c r="N41">
-        <v>0.1097960580325194</v>
+        <v>0.1158996171742827</v>
       </c>
       <c r="O41">
-        <v>0.108545998052558</v>
+        <v>0.1171461646481182</v>
       </c>
       <c r="P41">
-        <v>0.1083721541503955</v>
+        <v>0.1202864548120101</v>
       </c>
       <c r="Q41">
-        <v>0.1083970237198404</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.12075342129772609</v>
+      </c>
+      <c r="R41">
+        <v>0.1216011307785821</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>0.1043731368526334</v>
+        <v>0.1062366615481535</v>
       </c>
       <c r="C42">
-        <v>0.1165643448061762</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D42">
-        <v>0.120941320660191</v>
+        <v>0.1132124591506475</v>
       </c>
       <c r="E42">
-        <v>0.1194952659908395</v>
+        <v>0.12815299344748621</v>
       </c>
       <c r="F42">
-        <v>0.1115326654366049</v>
+        <v>0.1214965789600272</v>
       </c>
       <c r="G42">
-        <v>0.1103555201648455</v>
+        <v>0.1089930373807806</v>
       </c>
       <c r="H42">
-        <v>0.1030523656388864</v>
+        <v>0.1046151214718062</v>
       </c>
       <c r="I42">
-        <v>0.09566067181443408</v>
+        <v>0.10217693768455691</v>
       </c>
       <c r="J42">
-        <v>0.09578398150347799</v>
+        <v>9.6820866566854777E-2</v>
       </c>
       <c r="K42">
-        <v>0.09843937907419126</v>
+        <v>9.5970188345315524E-2</v>
       </c>
       <c r="L42">
-        <v>0.1011826412300454</v>
+        <v>9.73913829136792E-2</v>
       </c>
       <c r="M42">
-        <v>0.1014551828401483</v>
+        <v>9.5670865510631031E-2</v>
       </c>
       <c r="N42">
-        <v>0.1022694446896126</v>
+        <v>9.5744165175891266E-2</v>
       </c>
       <c r="O42">
-        <v>0.1017719779877868</v>
+        <v>9.7174392131522486E-2</v>
       </c>
       <c r="P42">
-        <v>0.1005915761860742</v>
+        <v>9.7747492216740187E-2</v>
       </c>
       <c r="Q42">
-        <v>0.09985753212969695</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>9.7690577180186144E-2</v>
+      </c>
+      <c r="R42">
+        <v>9.8535503671707464E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>0.1067686256152511</v>
+        <v>0.105558527019604</v>
       </c>
       <c r="C43">
-        <v>0.1166488210060977</v>
+        <v>0.11298752717561721</v>
       </c>
       <c r="D43">
-        <v>0.1202677963984483</v>
+        <v>0.11562436489869871</v>
       </c>
       <c r="E43">
-        <v>0.1181804758781907</v>
+        <v>0.1180865616861701</v>
       </c>
       <c r="F43">
-        <v>0.1119656350729256</v>
+        <v>0.11340538782522459</v>
       </c>
       <c r="G43">
-        <v>0.111344816316402</v>
+        <v>0.11094603464175069</v>
       </c>
       <c r="H43">
-        <v>0.1053801603033712</v>
+        <v>0.10183228737346491</v>
       </c>
       <c r="I43">
-        <v>0.09715855828241755</v>
+        <v>9.8695258547852563E-2</v>
       </c>
       <c r="J43">
-        <v>0.09767400811067799</v>
+        <v>9.6712560477649798E-2</v>
       </c>
       <c r="K43">
-        <v>0.09720079924262612</v>
+        <v>9.7820964736921812E-2</v>
       </c>
       <c r="L43">
-        <v>0.09779345705954656</v>
+        <v>0.1002037971922513</v>
       </c>
       <c r="M43">
-        <v>0.09828253945431852</v>
+        <v>9.7393899008806489E-2</v>
       </c>
       <c r="N43">
-        <v>0.09724373040824913</v>
+        <v>9.6914386338298159E-2</v>
       </c>
       <c r="O43">
-        <v>0.09797302055494861</v>
+        <v>9.6484386208275555E-2</v>
       </c>
       <c r="P43">
-        <v>0.0991073520120923</v>
+        <v>9.7894118480025383E-2</v>
       </c>
       <c r="Q43">
-        <v>0.09873463963269899</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.1160694160121382</v>
-      </c>
-      <c r="C44">
-        <v>0.1182821548742386</v>
-      </c>
-      <c r="D44">
-        <v>0.1166236874100363</v>
-      </c>
-      <c r="E44">
-        <v>0.1116838435030778</v>
-      </c>
-      <c r="F44">
-        <v>0.1134066400728571</v>
-      </c>
-      <c r="G44">
-        <v>0.1065550195736849</v>
-      </c>
-      <c r="H44">
-        <v>0.1026289176824021</v>
-      </c>
-      <c r="I44">
-        <v>0.1029874396942331</v>
-      </c>
-      <c r="J44">
-        <v>0.1053076596533017</v>
-      </c>
-      <c r="K44">
-        <v>0.1056041755545694</v>
-      </c>
-      <c r="L44">
-        <v>0.1034159334631091</v>
-      </c>
-      <c r="M44">
-        <v>0.1040668456509806</v>
-      </c>
-      <c r="N44">
-        <v>0.1031884197479186</v>
-      </c>
-      <c r="O44">
-        <v>0.1043110924704865</v>
-      </c>
-      <c r="P44">
-        <v>0.1060469353845587</v>
-      </c>
-      <c r="Q44">
-        <v>0.1092057866865436</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.1184501217489029</v>
-      </c>
-      <c r="C45">
-        <v>0.1182876750315514</v>
-      </c>
-      <c r="D45">
-        <v>0.1270062885211053</v>
-      </c>
-      <c r="E45">
-        <v>0.1219633890579051</v>
-      </c>
-      <c r="F45">
-        <v>0.1216990346494259</v>
-      </c>
-      <c r="G45">
-        <v>0.1178517041613216</v>
-      </c>
-      <c r="H45">
-        <v>0.1166554584987256</v>
-      </c>
-      <c r="I45">
-        <v>0.1155806003325335</v>
-      </c>
-      <c r="J45">
-        <v>0.1130979080090069</v>
-      </c>
-      <c r="K45">
-        <v>0.1145281588255732</v>
-      </c>
-      <c r="L45">
-        <v>0.1162958226703595</v>
-      </c>
-      <c r="M45">
-        <v>0.1160880473481839</v>
-      </c>
-      <c r="N45">
-        <v>0.1172218622792674</v>
-      </c>
-      <c r="O45">
-        <v>0.1200628941017145</v>
-      </c>
-      <c r="P45">
-        <v>0.1205106527540746</v>
-      </c>
-      <c r="Q45">
-        <v>0.1215533928498523</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.1064728866010351</v>
-      </c>
-      <c r="C46">
-        <v>0.1130214899866195</v>
-      </c>
-      <c r="D46">
-        <v>0.1275813881540055</v>
-      </c>
-      <c r="E46">
-        <v>0.1207061432456829</v>
-      </c>
-      <c r="F46">
-        <v>0.1080599993306307</v>
-      </c>
-      <c r="G46">
-        <v>0.1042813524143531</v>
-      </c>
-      <c r="H46">
-        <v>0.1015275482094735</v>
-      </c>
-      <c r="I46">
-        <v>0.09619074802278288</v>
-      </c>
-      <c r="J46">
-        <v>0.09567860856139092</v>
-      </c>
-      <c r="K46">
-        <v>0.09670218654371045</v>
-      </c>
-      <c r="L46">
-        <v>0.09529000347619011</v>
-      </c>
-      <c r="M46">
-        <v>0.09565254871852132</v>
-      </c>
-      <c r="N46">
-        <v>0.09700637706902809</v>
-      </c>
-      <c r="O46">
-        <v>0.09728686999769956</v>
-      </c>
-      <c r="P46">
-        <v>0.09727384599784435</v>
-      </c>
-      <c r="Q46">
-        <v>0.09838322184142759</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.1059783452784343</v>
-      </c>
-      <c r="C47">
-        <v>0.1162936509344983</v>
-      </c>
-      <c r="D47">
-        <v>0.1187724020639986</v>
-      </c>
-      <c r="E47">
-        <v>0.11337245401505</v>
-      </c>
-      <c r="F47">
-        <v>0.1116135508120838</v>
-      </c>
-      <c r="G47">
-        <v>0.1018080382300647</v>
-      </c>
-      <c r="H47">
-        <v>0.09885484624979202</v>
-      </c>
-      <c r="I47">
-        <v>0.0963308357159251</v>
-      </c>
-      <c r="J47">
-        <v>0.09714198790465997</v>
-      </c>
-      <c r="K47">
-        <v>0.09916427434897306</v>
-      </c>
-      <c r="L47">
-        <v>0.09701201984831469</v>
-      </c>
-      <c r="M47">
-        <v>0.09695021996161288</v>
-      </c>
-      <c r="N47">
-        <v>0.096919604555956</v>
-      </c>
-      <c r="O47">
-        <v>0.09833670611533028</v>
-      </c>
-      <c r="P47">
-        <v>0.09938011854517223</v>
-      </c>
-      <c r="Q47">
-        <v>0.1009401394409097</v>
+        <v>9.9234606512678417E-2</v>
+      </c>
+      <c r="R43">
+        <v>0.1002665188046679</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:R43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>